--- a/mirror/for/kievskaya-ploshchad/kp.xlsx
+++ b/mirror/for/kievskaya-ploshchad/kp.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прайс" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'КП'!$A$4:$P$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'КП'!$A$4:$P$249</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'КП'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D37" s="12">
-        <f>КП!J173</f>
+        <f>КП!J174</f>
         <v/>
       </c>
       <c r="E37" s="8">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="D39" s="12">
-        <f>КП!J183</f>
+        <f>КП!J184</f>
         <v/>
       </c>
       <c r="E39" s="8">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="D42" s="12">
-        <f>КП!J212</f>
+        <f>КП!J213</f>
         <v/>
       </c>
       <c r="E42" s="8">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="D43" s="12">
-        <f>КП!J220</f>
+        <f>КП!J221</f>
         <v/>
       </c>
       <c r="E43" s="8">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="D45" s="12">
-        <f>КП!J225</f>
+        <f>КП!J226</f>
         <v/>
       </c>
       <c r="E45" s="8">
@@ -1707,7 +1707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P248"/>
+  <dimension ref="A1:P249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="P94" s="17" t="inlineStr">
         <is>
-          <t>Релизы моделей на использование изображения входят в стоимость: 1 год, РФ, ваши каналы и объекты. Шире по договору. Расходы на моделей, свет, стилистов и реквизит идут по себестоимости без нашей скидки.</t>
+          <t>Релизы моделей на использование изображения входят в стоимость: 1 год, РФ, ваши каналы и объекты. Шире по договору. На моделей, свет, стилистов и реквизит скидка 10% не действует.</t>
         </is>
       </c>
     </row>
@@ -7051,9 +7051,8 @@
         <f>ROUND(F121*G121,0)</f>
         <v/>
       </c>
-      <c r="I121" s="34">
-        <f>Прайс!$B$6</f>
-        <v/>
+      <c r="I121" s="34" t="n">
+        <v>0</v>
       </c>
       <c r="J121" s="35">
         <f>ROUND(H121*(1-I121),0)</f>
@@ -7746,7 +7745,7 @@
       </c>
       <c r="P138" s="17" t="inlineStr">
         <is>
-          <t>Упаковку считаем после концепции: материал и конструкция коробки задают цену. Наполнение закупаем по бюджету заказчика без наценки. Работаем по списку блогеров заказчика или подбираем свой.</t>
+          <t>Упаковку считаем после концепции: материал и конструкция коробки задают цену. Наполнение закупаем по согласованному бюджету и чекам, закупка и логистика отдельной строкой. Работаем по списку блогеров заказчика или подбираем свой.</t>
         </is>
       </c>
     </row>
@@ -7917,7 +7916,7 @@
       <c r="C143" s="22" t="n"/>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Наполнение по согласованному списку</t>
+          <t xml:space="preserve">   Наполнение по согласованному списку, бюджет до 5 000 ₽</t>
         </is>
       </c>
       <c r="E143" s="22" t="inlineStr">
@@ -7966,7 +7965,7 @@
       <c r="C144" s="22" t="n"/>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Сборка и упаковка</t>
+          <t xml:space="preserve">   Закупка, проверка и логистика наполнения, 25% от бюджета</t>
         </is>
       </c>
       <c r="E144" s="22" t="inlineStr">
@@ -8011,12 +8010,12 @@
       <c r="C145" s="22" t="n"/>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Курьерская доставка по Москве, фото вручения</t>
+          <t xml:space="preserve">   Сборка и упаковка</t>
         </is>
       </c>
       <c r="E145" s="22" t="inlineStr">
         <is>
-          <t>адрес</t>
+          <t>бокс</t>
         </is>
       </c>
       <c r="F145" s="23" t="n">
@@ -8051,117 +8050,117 @@
       <c r="P145" s="8" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="15" t="n">
+      <c r="A146" s="22" t="n"/>
+      <c r="B146" s="22" t="n"/>
+      <c r="C146" s="22" t="n"/>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Курьерская доставка по Москве, фото вручения</t>
+        </is>
+      </c>
+      <c r="E146" s="22" t="inlineStr">
+        <is>
+          <t>адрес</t>
+        </is>
+      </c>
+      <c r="F146" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="G146" s="24">
+        <f>Прайс!E113</f>
+        <v/>
+      </c>
+      <c r="H146" s="25">
+        <f>ROUND(F146*G146,0)</f>
+        <v/>
+      </c>
+      <c r="I146" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="27">
+        <f>ROUND(H146*(1-I146),0)</f>
+        <v/>
+      </c>
+      <c r="K146" s="25">
+        <f>ROUND(J146*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L146" s="27">
+        <f>J146+K146</f>
+        <v/>
+      </c>
+      <c r="M146" s="8" t="n"/>
+      <c r="N146" s="8" t="n"/>
+      <c r="O146" s="22" t="n"/>
+      <c r="P146" s="8" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="B146" s="16" t="inlineStr">
+      <c r="B147" s="16" t="inlineStr">
         <is>
           <t>Брендированная вода</t>
         </is>
       </c>
-      <c r="C146" s="17" t="inlineStr">
+      <c r="C147" s="17" t="inlineStr">
         <is>
           <t>Времена Года, Венеция</t>
         </is>
       </c>
-      <c r="D146" s="18" t="inlineStr">
+      <c r="D147" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E146" s="17" t="n"/>
-      <c r="F146" s="17" t="n"/>
-      <c r="G146" s="17" t="n"/>
-      <c r="H146" s="17" t="n"/>
-      <c r="I146" s="17" t="n"/>
-      <c r="J146" s="17" t="n"/>
-      <c r="K146" s="17" t="n"/>
-      <c r="L146" s="17" t="n"/>
-      <c r="M146" s="17" t="n"/>
-      <c r="N146" s="17">
+      <c r="E147" s="17" t="n"/>
+      <c r="F147" s="17" t="n"/>
+      <c r="G147" s="17" t="n"/>
+      <c r="H147" s="17" t="n"/>
+      <c r="I147" s="17" t="n"/>
+      <c r="J147" s="17" t="n"/>
+      <c r="K147" s="17" t="n"/>
+      <c r="L147" s="17" t="n"/>
+      <c r="M147" s="17" t="n"/>
+      <c r="N147" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$7,"0%")&amp;", остаток "&amp;TEXT(1-Прайс!$B$7,"0%")&amp;" после акта"</f>
         <v/>
       </c>
-      <c r="O146" s="17">
+      <c r="O147" s="17">
         <f>Прайс!$B$10&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P146" s="17" t="inlineStr">
+      <c r="P147" s="17" t="inlineStr">
         <is>
           <t>Розлив у сертифицированного производителя, декларации и протоколы испытаний передаем с поставкой. Этикетку печатаем по вашему макету. Хранение при +5...+25 °C, вдали от солнца.</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="19" t="n"/>
-      <c r="B147" s="19" t="n"/>
-      <c r="C147" s="19" t="n"/>
-      <c r="D147" s="20" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="19" t="n"/>
+      <c r="B148" s="19" t="n"/>
+      <c r="C148" s="19" t="n"/>
+      <c r="D148" s="20" t="inlineStr">
         <is>
           <t>(1) Вода 0,33 л ПЭТ, партии 1 000 и 5 000 шт.</t>
         </is>
       </c>
-      <c r="E147" s="19" t="n"/>
-      <c r="F147" s="19" t="n"/>
-      <c r="G147" s="19" t="n"/>
-      <c r="H147" s="19" t="n"/>
-      <c r="I147" s="19" t="n"/>
-      <c r="J147" s="19" t="n"/>
-      <c r="K147" s="19" t="n"/>
-      <c r="L147" s="19" t="n"/>
-      <c r="M147" s="19" t="inlineStr">
+      <c r="E148" s="19" t="n"/>
+      <c r="F148" s="19" t="n"/>
+      <c r="G148" s="19" t="n"/>
+      <c r="H148" s="19" t="n"/>
+      <c r="I148" s="19" t="n"/>
+      <c r="J148" s="19" t="n"/>
+      <c r="K148" s="19" t="n"/>
+      <c r="L148" s="19" t="n"/>
+      <c r="M148" s="19" t="inlineStr">
         <is>
           <t>10 р.д. после утверждения этикетки, срок годности 12 мес.</t>
         </is>
       </c>
-      <c r="N147" s="19" t="n"/>
-      <c r="O147" s="19" t="n"/>
-      <c r="P147" s="19" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="22" t="n"/>
-      <c r="B148" s="22" t="n"/>
-      <c r="C148" s="22" t="n"/>
-      <c r="D148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Вода негазированная 0,33 л ПЭТ, полноцветная этикетка, партия 1 000</t>
-        </is>
-      </c>
-      <c r="E148" s="22" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F148" s="23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G148" s="24">
-        <f>Прайс!E113</f>
-        <v/>
-      </c>
-      <c r="H148" s="25">
-        <f>ROUND(F148*G148,0)</f>
-        <v/>
-      </c>
-      <c r="I148" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" s="27">
-        <f>ROUND(H148*(1-I148),0)</f>
-        <v/>
-      </c>
-      <c r="K148" s="25">
-        <f>ROUND(J148*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L148" s="27">
-        <f>J148+K148</f>
-        <v/>
-      </c>
-      <c r="M148" s="8" t="n"/>
-      <c r="N148" s="8" t="n"/>
-      <c r="O148" s="22" t="n"/>
-      <c r="P148" s="8" t="n"/>
+      <c r="N148" s="19" t="n"/>
+      <c r="O148" s="19" t="n"/>
+      <c r="P148" s="19" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="22" t="n"/>
@@ -8169,7 +8168,7 @@
       <c r="C149" s="22" t="n"/>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Вода негазированная 0,33 л ПЭТ, полноцветная этикетка, партия 5 000</t>
+          <t xml:space="preserve">   Вода негазированная 0,33 л ПЭТ, полноцветная этикетка, партия 1 000</t>
         </is>
       </c>
       <c r="E149" s="22" t="inlineStr">
@@ -8178,7 +8177,7 @@
         </is>
       </c>
       <c r="F149" s="23" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="G149" s="24">
         <f>Прайс!E114</f>
@@ -8214,19 +8213,19 @@
       <c r="C150" s="22" t="n"/>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Доставка до объекта по Москве</t>
+          <t xml:space="preserve">   Вода негазированная 0,33 л ПЭТ, полноцветная этикетка, партия 5 000</t>
         </is>
       </c>
       <c r="E150" s="22" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="F150" s="23" t="n">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="G150" s="24">
-        <f>Прайс!E117</f>
+        <f>Прайс!E115</f>
         <v/>
       </c>
       <c r="H150" s="25">
@@ -8251,82 +8250,82 @@
       <c r="M150" s="8" t="n"/>
       <c r="N150" s="8" t="n"/>
       <c r="O150" s="22" t="n"/>
-      <c r="P150" s="8" t="inlineStr">
+      <c r="P150" s="8" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="22" t="n"/>
+      <c r="B151" s="22" t="n"/>
+      <c r="C151" s="22" t="n"/>
+      <c r="D151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Доставка до объекта по Москве</t>
+        </is>
+      </c>
+      <c r="E151" s="22" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="F151" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="24">
+        <f>Прайс!E118</f>
+        <v/>
+      </c>
+      <c r="H151" s="25">
+        <f>ROUND(F151*G151,0)</f>
+        <v/>
+      </c>
+      <c r="I151" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="27">
+        <f>ROUND(H151*(1-I151),0)</f>
+        <v/>
+      </c>
+      <c r="K151" s="25">
+        <f>ROUND(J151*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L151" s="27">
+        <f>J151+K151</f>
+        <v/>
+      </c>
+      <c r="M151" s="8" t="n"/>
+      <c r="N151" s="8" t="n"/>
+      <c r="O151" s="22" t="n"/>
+      <c r="P151" s="8" t="inlineStr">
         <is>
           <t>на партию</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="19" t="n"/>
-      <c r="B151" s="19" t="n"/>
-      <c r="C151" s="19" t="n"/>
-      <c r="D151" s="20" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="19" t="n"/>
+      <c r="B152" s="19" t="n"/>
+      <c r="C152" s="19" t="n"/>
+      <c r="D152" s="20" t="inlineStr">
         <is>
           <t>(2) Вода 0,33 л в стекле, партии 1 000 и 5 000 шт.</t>
         </is>
       </c>
-      <c r="E151" s="19" t="n"/>
-      <c r="F151" s="19" t="n"/>
-      <c r="G151" s="19" t="n"/>
-      <c r="H151" s="19" t="n"/>
-      <c r="I151" s="19" t="n"/>
-      <c r="J151" s="19" t="n"/>
-      <c r="K151" s="19" t="n"/>
-      <c r="L151" s="19" t="n"/>
-      <c r="M151" s="19" t="inlineStr">
+      <c r="E152" s="19" t="n"/>
+      <c r="F152" s="19" t="n"/>
+      <c r="G152" s="19" t="n"/>
+      <c r="H152" s="19" t="n"/>
+      <c r="I152" s="19" t="n"/>
+      <c r="J152" s="19" t="n"/>
+      <c r="K152" s="19" t="n"/>
+      <c r="L152" s="19" t="n"/>
+      <c r="M152" s="19" t="inlineStr">
         <is>
           <t>15 р.д. после утверждения этикетки, срок годности 24 мес.</t>
         </is>
       </c>
-      <c r="N151" s="19" t="n"/>
-      <c r="O151" s="19" t="n"/>
-      <c r="P151" s="19" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="22" t="n"/>
-      <c r="B152" s="22" t="n"/>
-      <c r="C152" s="22" t="n"/>
-      <c r="D152" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Вода 0,33 л в стекле, полноцветная этикетка, партия 1 000</t>
-        </is>
-      </c>
-      <c r="E152" s="22" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F152" s="23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G152" s="24">
-        <f>Прайс!E115</f>
-        <v/>
-      </c>
-      <c r="H152" s="25">
-        <f>ROUND(F152*G152,0)</f>
-        <v/>
-      </c>
-      <c r="I152" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="27">
-        <f>ROUND(H152*(1-I152),0)</f>
-        <v/>
-      </c>
-      <c r="K152" s="25">
-        <f>ROUND(J152*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L152" s="27">
-        <f>J152+K152</f>
-        <v/>
-      </c>
-      <c r="M152" s="8" t="n"/>
-      <c r="N152" s="8" t="n"/>
-      <c r="O152" s="22" t="n"/>
-      <c r="P152" s="8" t="n"/>
+      <c r="N152" s="19" t="n"/>
+      <c r="O152" s="19" t="n"/>
+      <c r="P152" s="19" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="22" t="n"/>
@@ -8334,7 +8333,7 @@
       <c r="C153" s="22" t="n"/>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Вода 0,33 л в стекле, полноцветная этикетка, партия 5 000</t>
+          <t xml:space="preserve">   Вода 0,33 л в стекле, полноцветная этикетка, партия 1 000</t>
         </is>
       </c>
       <c r="E153" s="22" t="inlineStr">
@@ -8343,7 +8342,7 @@
         </is>
       </c>
       <c r="F153" s="23" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="G153" s="24">
         <f>Прайс!E116</f>
@@ -8379,16 +8378,16 @@
       <c r="C154" s="22" t="n"/>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Доставка до объекта по Москве</t>
+          <t xml:space="preserve">   Вода 0,33 л в стекле, полноцветная этикетка, партия 5 000</t>
         </is>
       </c>
       <c r="E154" s="22" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="F154" s="23" t="n">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="G154" s="24">
         <f>Прайс!E117</f>
@@ -8416,102 +8415,98 @@
       <c r="M154" s="8" t="n"/>
       <c r="N154" s="8" t="n"/>
       <c r="O154" s="22" t="n"/>
-      <c r="P154" s="8" t="inlineStr">
+      <c r="P154" s="8" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="22" t="n"/>
+      <c r="B155" s="22" t="n"/>
+      <c r="C155" s="22" t="n"/>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Доставка до объекта по Москве</t>
+        </is>
+      </c>
+      <c r="E155" s="22" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="F155" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="24">
+        <f>Прайс!E118</f>
+        <v/>
+      </c>
+      <c r="H155" s="25">
+        <f>ROUND(F155*G155,0)</f>
+        <v/>
+      </c>
+      <c r="I155" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="27">
+        <f>ROUND(H155*(1-I155),0)</f>
+        <v/>
+      </c>
+      <c r="K155" s="25">
+        <f>ROUND(J155*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L155" s="27">
+        <f>J155+K155</f>
+        <v/>
+      </c>
+      <c r="M155" s="8" t="n"/>
+      <c r="N155" s="8" t="n"/>
+      <c r="O155" s="22" t="n"/>
+      <c r="P155" s="8" t="inlineStr">
         <is>
           <t>на партию</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="15" t="n">
+    <row r="156">
+      <c r="A156" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="B155" s="16" t="inlineStr">
+      <c r="B156" s="16" t="inlineStr">
         <is>
           <t>Свечи и диффузоры</t>
         </is>
       </c>
-      <c r="C155" s="17" t="inlineStr">
+      <c r="C156" s="17" t="inlineStr">
         <is>
           <t>Времена Года, Венеция</t>
         </is>
       </c>
-      <c r="D155" s="18" t="inlineStr">
+      <c r="D156" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E155" s="17" t="n"/>
-      <c r="F155" s="17" t="n"/>
-      <c r="G155" s="17" t="n"/>
-      <c r="H155" s="17" t="n"/>
-      <c r="I155" s="17" t="n"/>
-      <c r="J155" s="17" t="n"/>
-      <c r="K155" s="17" t="n"/>
-      <c r="L155" s="17" t="n"/>
-      <c r="M155" s="17" t="n"/>
-      <c r="N155" s="17">
+      <c r="E156" s="17" t="n"/>
+      <c r="F156" s="17" t="n"/>
+      <c r="G156" s="17" t="n"/>
+      <c r="H156" s="17" t="n"/>
+      <c r="I156" s="17" t="n"/>
+      <c r="J156" s="17" t="n"/>
+      <c r="K156" s="17" t="n"/>
+      <c r="L156" s="17" t="n"/>
+      <c r="M156" s="17" t="n"/>
+      <c r="N156" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$7,"0%")&amp;", остаток "&amp;TEXT(1-Прайс!$B$7,"0%")&amp;" после акта"</f>
         <v/>
       </c>
-      <c r="O155" s="17">
+      <c r="O156" s="17">
         <f>Прайс!$B$10&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P155" s="17" t="inlineStr">
+      <c r="P156" s="17" t="inlineStr">
         <is>
           <t>Соевый или кокосовый воск, отдушки с сертификатами IFRA. Мыло и кремы производятся по декларации ЕАЭС производителя. Срок годности свечей и диффузоров 24 мес., мыла 18 мес.</t>
         </is>
       </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="19" t="n"/>
-      <c r="B156" s="19" t="n"/>
-      <c r="C156" s="19" t="n"/>
-      <c r="D156" s="20" t="inlineStr">
-        <is>
-          <t>(1) Разработка эксклюзивного аромата, 3 варианта</t>
-        </is>
-      </c>
-      <c r="E156" s="19" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="F156" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G156" s="32">
-        <f>Прайс!E118</f>
-        <v/>
-      </c>
-      <c r="H156" s="33">
-        <f>ROUND(F156*G156,0)</f>
-        <v/>
-      </c>
-      <c r="I156" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" s="35">
-        <f>ROUND(H156*(1-I156),0)</f>
-        <v/>
-      </c>
-      <c r="K156" s="33">
-        <f>ROUND(J156*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L156" s="35">
-        <f>J156+K156</f>
-        <v/>
-      </c>
-      <c r="M156" s="19" t="inlineStr">
-        <is>
-          <t>15 р.д., образцы ароматов высылаем</t>
-        </is>
-      </c>
-      <c r="N156" s="19" t="n"/>
-      <c r="O156" s="19" t="n"/>
-      <c r="P156" s="19" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="19" t="n"/>
@@ -8519,20 +8514,43 @@
       <c r="C157" s="19" t="n"/>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>(2) Свеча 200 мл, партии 100 и 300 шт.</t>
-        </is>
-      </c>
-      <c r="E157" s="19" t="n"/>
-      <c r="F157" s="19" t="n"/>
-      <c r="G157" s="19" t="n"/>
-      <c r="H157" s="19" t="n"/>
-      <c r="I157" s="19" t="n"/>
-      <c r="J157" s="19" t="n"/>
-      <c r="K157" s="19" t="n"/>
-      <c r="L157" s="19" t="n"/>
+          <t>(1) Разработка эксклюзивного аромата, 3 варианта</t>
+        </is>
+      </c>
+      <c r="E157" s="19" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="F157" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="32">
+        <f>Прайс!E119</f>
+        <v/>
+      </c>
+      <c r="H157" s="33">
+        <f>ROUND(F157*G157,0)</f>
+        <v/>
+      </c>
+      <c r="I157" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="35">
+        <f>ROUND(H157*(1-I157),0)</f>
+        <v/>
+      </c>
+      <c r="K157" s="33">
+        <f>ROUND(J157*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L157" s="35">
+        <f>J157+K157</f>
+        <v/>
+      </c>
       <c r="M157" s="19" t="inlineStr">
         <is>
-          <t>20 р.д. после утверждения аромата и упаковки</t>
+          <t>15 р.д., образцы ароматов высылаем</t>
         </is>
       </c>
       <c r="N157" s="19" t="n"/>
@@ -8540,49 +8558,30 @@
       <c r="P157" s="19" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="22" t="n"/>
-      <c r="B158" s="22" t="n"/>
-      <c r="C158" s="22" t="n"/>
-      <c r="D158" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Свеча 200 мл в стекле с крышкой, брендированная коробка, партия 100</t>
-        </is>
-      </c>
-      <c r="E158" s="22" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F158" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="G158" s="24">
-        <f>Прайс!E119</f>
-        <v/>
-      </c>
-      <c r="H158" s="25">
-        <f>ROUND(F158*G158,0)</f>
-        <v/>
-      </c>
-      <c r="I158" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" s="27">
-        <f>ROUND(H158*(1-I158),0)</f>
-        <v/>
-      </c>
-      <c r="K158" s="25">
-        <f>ROUND(J158*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L158" s="27">
-        <f>J158+K158</f>
-        <v/>
-      </c>
-      <c r="M158" s="8" t="n"/>
-      <c r="N158" s="8" t="n"/>
-      <c r="O158" s="22" t="n"/>
-      <c r="P158" s="8" t="n"/>
+      <c r="A158" s="19" t="n"/>
+      <c r="B158" s="19" t="n"/>
+      <c r="C158" s="19" t="n"/>
+      <c r="D158" s="20" t="inlineStr">
+        <is>
+          <t>(2) Свеча 200 мл, партии 100 и 300 шт.</t>
+        </is>
+      </c>
+      <c r="E158" s="19" t="n"/>
+      <c r="F158" s="19" t="n"/>
+      <c r="G158" s="19" t="n"/>
+      <c r="H158" s="19" t="n"/>
+      <c r="I158" s="19" t="n"/>
+      <c r="J158" s="19" t="n"/>
+      <c r="K158" s="19" t="n"/>
+      <c r="L158" s="19" t="n"/>
+      <c r="M158" s="19" t="inlineStr">
+        <is>
+          <t>20 р.д. после утверждения аромата и упаковки</t>
+        </is>
+      </c>
+      <c r="N158" s="19" t="n"/>
+      <c r="O158" s="19" t="n"/>
+      <c r="P158" s="19" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="22" t="n"/>
@@ -8590,7 +8589,7 @@
       <c r="C159" s="22" t="n"/>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Свеча 200 мл в стекле с крышкой, брендированная коробка, партия 300</t>
+          <t xml:space="preserve">   Свеча 200 мл в стекле с крышкой, брендированная коробка, партия 100</t>
         </is>
       </c>
       <c r="E159" s="22" t="inlineStr">
@@ -8599,7 +8598,7 @@
         </is>
       </c>
       <c r="F159" s="23" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G159" s="24">
         <f>Прайс!E120</f>
@@ -8630,91 +8629,91 @@
       <c r="P159" s="8" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="19" t="n"/>
-      <c r="B160" s="19" t="n"/>
-      <c r="C160" s="19" t="n"/>
-      <c r="D160" s="20" t="inlineStr">
+      <c r="A160" s="22" t="n"/>
+      <c r="B160" s="22" t="n"/>
+      <c r="C160" s="22" t="n"/>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Свеча 200 мл в стекле с крышкой, брендированная коробка, партия 300</t>
+        </is>
+      </c>
+      <c r="E160" s="22" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F160" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="G160" s="24">
+        <f>Прайс!E121</f>
+        <v/>
+      </c>
+      <c r="H160" s="25">
+        <f>ROUND(F160*G160,0)</f>
+        <v/>
+      </c>
+      <c r="I160" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="27">
+        <f>ROUND(H160*(1-I160),0)</f>
+        <v/>
+      </c>
+      <c r="K160" s="25">
+        <f>ROUND(J160*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L160" s="27">
+        <f>J160+K160</f>
+        <v/>
+      </c>
+      <c r="M160" s="8" t="n"/>
+      <c r="N160" s="8" t="n"/>
+      <c r="O160" s="22" t="n"/>
+      <c r="P160" s="8" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="19" t="n"/>
+      <c r="B161" s="19" t="n"/>
+      <c r="C161" s="19" t="n"/>
+      <c r="D161" s="20" t="inlineStr">
         <is>
           <t>(3) Диффузор 100 мл, партия 100 шт.</t>
         </is>
       </c>
-      <c r="E160" s="9" t="inlineStr">
+      <c r="E161" s="9" t="inlineStr">
         <is>
           <t>итого</t>
         </is>
       </c>
-      <c r="F160" s="19" t="n"/>
-      <c r="G160" s="19" t="n"/>
-      <c r="H160" s="21">
-        <f>SUM(H161:H162)</f>
-        <v/>
-      </c>
-      <c r="I160" s="19" t="n"/>
-      <c r="J160" s="21">
-        <f>SUM(J161:J162)</f>
-        <v/>
-      </c>
-      <c r="K160" s="21">
-        <f>SUM(K161:K162)</f>
-        <v/>
-      </c>
-      <c r="L160" s="21">
-        <f>SUM(L161:L162)</f>
-        <v/>
-      </c>
-      <c r="M160" s="19" t="inlineStr">
+      <c r="F161" s="19" t="n"/>
+      <c r="G161" s="19" t="n"/>
+      <c r="H161" s="21">
+        <f>SUM(H162:H163)</f>
+        <v/>
+      </c>
+      <c r="I161" s="19" t="n"/>
+      <c r="J161" s="21">
+        <f>SUM(J162:J163)</f>
+        <v/>
+      </c>
+      <c r="K161" s="21">
+        <f>SUM(K162:K163)</f>
+        <v/>
+      </c>
+      <c r="L161" s="21">
+        <f>SUM(L162:L163)</f>
+        <v/>
+      </c>
+      <c r="M161" s="19" t="inlineStr">
         <is>
           <t>20 р.д. после утверждения аромата и упаковки</t>
         </is>
       </c>
-      <c r="N160" s="19" t="n"/>
-      <c r="O160" s="19" t="n"/>
-      <c r="P160" s="19" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="22" t="n"/>
-      <c r="B161" s="22" t="n"/>
-      <c r="C161" s="22" t="n"/>
-      <c r="D161" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Диффузор 100 мл с палочками, брендированная упаковка, партия 100</t>
-        </is>
-      </c>
-      <c r="E161" s="22" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F161" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="G161" s="24">
-        <f>Прайс!E121</f>
-        <v/>
-      </c>
-      <c r="H161" s="25">
-        <f>ROUND(F161*G161,0)</f>
-        <v/>
-      </c>
-      <c r="I161" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" s="27">
-        <f>ROUND(H161*(1-I161),0)</f>
-        <v/>
-      </c>
-      <c r="K161" s="25">
-        <f>ROUND(J161*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L161" s="27">
-        <f>J161+K161</f>
-        <v/>
-      </c>
-      <c r="M161" s="8" t="n"/>
-      <c r="N161" s="8" t="n"/>
-      <c r="O161" s="22" t="n"/>
-      <c r="P161" s="8" t="n"/>
+      <c r="N161" s="19" t="n"/>
+      <c r="O161" s="19" t="n"/>
+      <c r="P161" s="19" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="22" t="n"/>
@@ -8722,19 +8721,19 @@
       <c r="C162" s="22" t="n"/>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Доставка по Москве</t>
+          <t xml:space="preserve">   Диффузор 100 мл с палочками, брендированная упаковка, партия 100</t>
         </is>
       </c>
       <c r="E162" s="22" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="F162" s="23" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G162" s="24">
-        <f>Прайс!E123</f>
+        <f>Прайс!E122</f>
         <v/>
       </c>
       <c r="H162" s="25">
@@ -8759,98 +8758,98 @@
       <c r="M162" s="8" t="n"/>
       <c r="N162" s="8" t="n"/>
       <c r="O162" s="22" t="n"/>
-      <c r="P162" s="8" t="inlineStr">
+      <c r="P162" s="8" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="22" t="n"/>
+      <c r="B163" s="22" t="n"/>
+      <c r="C163" s="22" t="n"/>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Доставка по Москве</t>
+        </is>
+      </c>
+      <c r="E163" s="22" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="F163" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="24">
+        <f>Прайс!E124</f>
+        <v/>
+      </c>
+      <c r="H163" s="25">
+        <f>ROUND(F163*G163,0)</f>
+        <v/>
+      </c>
+      <c r="I163" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="27">
+        <f>ROUND(H163*(1-I163),0)</f>
+        <v/>
+      </c>
+      <c r="K163" s="25">
+        <f>ROUND(J163*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L163" s="27">
+        <f>J163+K163</f>
+        <v/>
+      </c>
+      <c r="M163" s="8" t="n"/>
+      <c r="N163" s="8" t="n"/>
+      <c r="O163" s="22" t="n"/>
+      <c r="P163" s="8" t="inlineStr">
         <is>
           <t>до Автозаводской, 18</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="19" t="n"/>
-      <c r="B163" s="19" t="n"/>
-      <c r="C163" s="19" t="n"/>
-      <c r="D163" s="20" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="19" t="n"/>
+      <c r="B164" s="19" t="n"/>
+      <c r="C164" s="19" t="n"/>
+      <c r="D164" s="20" t="inlineStr">
         <is>
           <t>(4) Мыло жидкое 250 мл, партия 300 шт.</t>
         </is>
       </c>
-      <c r="E163" s="9" t="inlineStr">
+      <c r="E164" s="9" t="inlineStr">
         <is>
           <t>итого</t>
         </is>
       </c>
-      <c r="F163" s="19" t="n"/>
-      <c r="G163" s="19" t="n"/>
-      <c r="H163" s="21">
-        <f>SUM(H164:H165)</f>
-        <v/>
-      </c>
-      <c r="I163" s="19" t="n"/>
-      <c r="J163" s="21">
-        <f>SUM(J164:J165)</f>
-        <v/>
-      </c>
-      <c r="K163" s="21">
-        <f>SUM(K164:K165)</f>
-        <v/>
-      </c>
-      <c r="L163" s="21">
-        <f>SUM(L164:L165)</f>
-        <v/>
-      </c>
-      <c r="M163" s="19" t="inlineStr">
+      <c r="F164" s="19" t="n"/>
+      <c r="G164" s="19" t="n"/>
+      <c r="H164" s="21">
+        <f>SUM(H165:H166)</f>
+        <v/>
+      </c>
+      <c r="I164" s="19" t="n"/>
+      <c r="J164" s="21">
+        <f>SUM(J165:J166)</f>
+        <v/>
+      </c>
+      <c r="K164" s="21">
+        <f>SUM(K165:K166)</f>
+        <v/>
+      </c>
+      <c r="L164" s="21">
+        <f>SUM(L165:L166)</f>
+        <v/>
+      </c>
+      <c r="M164" s="19" t="inlineStr">
         <is>
           <t>20 р.д. после утверждения аромата и этикетки</t>
         </is>
       </c>
-      <c r="N163" s="19" t="n"/>
-      <c r="O163" s="19" t="n"/>
-      <c r="P163" s="19" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="22" t="n"/>
-      <c r="B164" s="22" t="n"/>
-      <c r="C164" s="22" t="n"/>
-      <c r="D164" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Мыло жидкое 250 мл с дозатором, брендированная этикетка, партия 300</t>
-        </is>
-      </c>
-      <c r="E164" s="22" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F164" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="G164" s="24">
-        <f>Прайс!E122</f>
-        <v/>
-      </c>
-      <c r="H164" s="25">
-        <f>ROUND(F164*G164,0)</f>
-        <v/>
-      </c>
-      <c r="I164" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" s="27">
-        <f>ROUND(H164*(1-I164),0)</f>
-        <v/>
-      </c>
-      <c r="K164" s="25">
-        <f>ROUND(J164*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L164" s="27">
-        <f>J164+K164</f>
-        <v/>
-      </c>
-      <c r="M164" s="8" t="n"/>
-      <c r="N164" s="8" t="n"/>
-      <c r="O164" s="22" t="n"/>
-      <c r="P164" s="8" t="n"/>
+      <c r="N164" s="19" t="n"/>
+      <c r="O164" s="19" t="n"/>
+      <c r="P164" s="19" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="22" t="n"/>
@@ -8858,16 +8857,16 @@
       <c r="C165" s="22" t="n"/>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Доставка по Москве</t>
+          <t xml:space="preserve">   Мыло жидкое 250 мл с дозатором, брендированная этикетка, партия 300</t>
         </is>
       </c>
       <c r="E165" s="22" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="F165" s="23" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="G165" s="24">
         <f>Прайс!E123</f>
@@ -8895,124 +8894,124 @@
       <c r="M165" s="8" t="n"/>
       <c r="N165" s="8" t="n"/>
       <c r="O165" s="22" t="n"/>
-      <c r="P165" s="8" t="inlineStr">
+      <c r="P165" s="8" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="22" t="n"/>
+      <c r="B166" s="22" t="n"/>
+      <c r="C166" s="22" t="n"/>
+      <c r="D166" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Доставка по Москве</t>
+        </is>
+      </c>
+      <c r="E166" s="22" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="F166" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="24">
+        <f>Прайс!E124</f>
+        <v/>
+      </c>
+      <c r="H166" s="25">
+        <f>ROUND(F166*G166,0)</f>
+        <v/>
+      </c>
+      <c r="I166" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="27">
+        <f>ROUND(H166*(1-I166),0)</f>
+        <v/>
+      </c>
+      <c r="K166" s="25">
+        <f>ROUND(J166*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L166" s="27">
+        <f>J166+K166</f>
+        <v/>
+      </c>
+      <c r="M166" s="8" t="n"/>
+      <c r="N166" s="8" t="n"/>
+      <c r="O166" s="22" t="n"/>
+      <c r="P166" s="8" t="inlineStr">
         <is>
           <t>до Автозаводской, 18</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="15" t="n">
+    <row r="167">
+      <c r="A167" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="B166" s="16" t="inlineStr">
+      <c r="B167" s="16" t="inlineStr">
         <is>
           <t>Шоколад</t>
         </is>
       </c>
-      <c r="C166" s="17" t="inlineStr">
+      <c r="C167" s="17" t="inlineStr">
         <is>
           <t>Времена Года, Венеция</t>
         </is>
       </c>
-      <c r="D166" s="18" t="inlineStr">
+      <c r="D167" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E166" s="17" t="n"/>
-      <c r="F166" s="17" t="n"/>
-      <c r="G166" s="17" t="n"/>
-      <c r="H166" s="17" t="n"/>
-      <c r="I166" s="17" t="n"/>
-      <c r="J166" s="17" t="n"/>
-      <c r="K166" s="17" t="n"/>
-      <c r="L166" s="17" t="n"/>
-      <c r="M166" s="17" t="n"/>
-      <c r="N166" s="17">
+      <c r="E167" s="17" t="n"/>
+      <c r="F167" s="17" t="n"/>
+      <c r="G167" s="17" t="n"/>
+      <c r="H167" s="17" t="n"/>
+      <c r="I167" s="17" t="n"/>
+      <c r="J167" s="17" t="n"/>
+      <c r="K167" s="17" t="n"/>
+      <c r="L167" s="17" t="n"/>
+      <c r="M167" s="17" t="n"/>
+      <c r="N167" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$7,"0%")&amp;", остаток "&amp;TEXT(1-Прайс!$B$7,"0%")&amp;" после акта"</f>
         <v/>
       </c>
-      <c r="O166" s="17">
+      <c r="O167" s="17">
         <f>Прайс!$B$10&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P166" s="17" t="inlineStr">
+      <c r="P167" s="17" t="inlineStr">
         <is>
           <t>Минимальная партия 100 шт. Декларации производителя передаем с поставкой. Хранение при +15...+18 °C. Доставка по Москве 6 500 ₽ за рейс.</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="19" t="n"/>
-      <c r="B167" s="19" t="n"/>
-      <c r="C167" s="19" t="n"/>
-      <c r="D167" s="20" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="19" t="n"/>
+      <c r="B168" s="19" t="n"/>
+      <c r="C168" s="19" t="n"/>
+      <c r="D168" s="20" t="inlineStr">
         <is>
           <t>(1) Плитка 50 г в обертке с логотипом, партии 200 и 1 000 шт.</t>
         </is>
       </c>
-      <c r="E167" s="19" t="n"/>
-      <c r="F167" s="19" t="n"/>
-      <c r="G167" s="19" t="n"/>
-      <c r="H167" s="19" t="n"/>
-      <c r="I167" s="19" t="n"/>
-      <c r="J167" s="19" t="n"/>
-      <c r="K167" s="19" t="n"/>
-      <c r="L167" s="19" t="n"/>
-      <c r="M167" s="19" t="inlineStr">
+      <c r="E168" s="19" t="n"/>
+      <c r="F168" s="19" t="n"/>
+      <c r="G168" s="19" t="n"/>
+      <c r="H168" s="19" t="n"/>
+      <c r="I168" s="19" t="n"/>
+      <c r="J168" s="19" t="n"/>
+      <c r="K168" s="19" t="n"/>
+      <c r="L168" s="19" t="n"/>
+      <c r="M168" s="19" t="inlineStr">
         <is>
           <t>10 р.д. после утверждения макета, срок годности 9 мес.</t>
         </is>
       </c>
-      <c r="N167" s="19" t="n"/>
-      <c r="O167" s="19" t="n"/>
-      <c r="P167" s="19" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="22" t="n"/>
-      <c r="B168" s="22" t="n"/>
-      <c r="C168" s="22" t="n"/>
-      <c r="D168" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Плитка шоколада 50 г, индивидуальная обертка с логотипом, партия 200</t>
-        </is>
-      </c>
-      <c r="E168" s="22" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F168" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="G168" s="24">
-        <f>Прайс!E124</f>
-        <v/>
-      </c>
-      <c r="H168" s="25">
-        <f>ROUND(F168*G168,0)</f>
-        <v/>
-      </c>
-      <c r="I168" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="27">
-        <f>ROUND(H168*(1-I168),0)</f>
-        <v/>
-      </c>
-      <c r="K168" s="25">
-        <f>ROUND(J168*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L168" s="27">
-        <f>J168+K168</f>
-        <v/>
-      </c>
-      <c r="M168" s="8" t="n"/>
-      <c r="N168" s="8" t="n"/>
-      <c r="O168" s="22" t="n"/>
-      <c r="P168" s="8" t="n"/>
+      <c r="N168" s="19" t="n"/>
+      <c r="O168" s="19" t="n"/>
+      <c r="P168" s="19" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="22" t="n"/>
@@ -9020,7 +9019,7 @@
       <c r="C169" s="22" t="n"/>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Плитка шоколада 50 г, индивидуальная обертка с логотипом, партия 1 000</t>
+          <t xml:space="preserve">   Плитка шоколада 50 г, индивидуальная обертка с логотипом, партия 200</t>
         </is>
       </c>
       <c r="E169" s="22" t="inlineStr">
@@ -9029,7 +9028,7 @@
         </is>
       </c>
       <c r="F169" s="23" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G169" s="24">
         <f>Прайс!E125</f>
@@ -9060,75 +9059,75 @@
       <c r="P169" s="8" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="19" t="n"/>
-      <c r="B170" s="19" t="n"/>
-      <c r="C170" s="19" t="n"/>
-      <c r="D170" s="20" t="inlineStr">
+      <c r="A170" s="22" t="n"/>
+      <c r="B170" s="22" t="n"/>
+      <c r="C170" s="22" t="n"/>
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Плитка шоколада 50 г, индивидуальная обертка с логотипом, партия 1 000</t>
+        </is>
+      </c>
+      <c r="E170" s="22" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F170" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G170" s="24">
+        <f>Прайс!E126</f>
+        <v/>
+      </c>
+      <c r="H170" s="25">
+        <f>ROUND(F170*G170,0)</f>
+        <v/>
+      </c>
+      <c r="I170" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="27">
+        <f>ROUND(H170*(1-I170),0)</f>
+        <v/>
+      </c>
+      <c r="K170" s="25">
+        <f>ROUND(J170*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L170" s="27">
+        <f>J170+K170</f>
+        <v/>
+      </c>
+      <c r="M170" s="8" t="n"/>
+      <c r="N170" s="8" t="n"/>
+      <c r="O170" s="22" t="n"/>
+      <c r="P170" s="8" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="19" t="n"/>
+      <c r="B171" s="19" t="n"/>
+      <c r="C171" s="19" t="n"/>
+      <c r="D171" s="20" t="inlineStr">
         <is>
           <t>(2) Набор 9 конфет в брендированной коробке, партии 200 и 1 000 шт.</t>
         </is>
       </c>
-      <c r="E170" s="19" t="n"/>
-      <c r="F170" s="19" t="n"/>
-      <c r="G170" s="19" t="n"/>
-      <c r="H170" s="19" t="n"/>
-      <c r="I170" s="19" t="n"/>
-      <c r="J170" s="19" t="n"/>
-      <c r="K170" s="19" t="n"/>
-      <c r="L170" s="19" t="n"/>
-      <c r="M170" s="19" t="inlineStr">
+      <c r="E171" s="19" t="n"/>
+      <c r="F171" s="19" t="n"/>
+      <c r="G171" s="19" t="n"/>
+      <c r="H171" s="19" t="n"/>
+      <c r="I171" s="19" t="n"/>
+      <c r="J171" s="19" t="n"/>
+      <c r="K171" s="19" t="n"/>
+      <c r="L171" s="19" t="n"/>
+      <c r="M171" s="19" t="inlineStr">
         <is>
           <t>15 р.д. после утверждения макета, срок годности 4 мес.</t>
         </is>
       </c>
-      <c r="N170" s="19" t="n"/>
-      <c r="O170" s="19" t="n"/>
-      <c r="P170" s="19" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="22" t="n"/>
-      <c r="B171" s="22" t="n"/>
-      <c r="C171" s="22" t="n"/>
-      <c r="D171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Набор 9 конфет в брендированной коробке, партия 200</t>
-        </is>
-      </c>
-      <c r="E171" s="22" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F171" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="G171" s="24">
-        <f>Прайс!E126</f>
-        <v/>
-      </c>
-      <c r="H171" s="25">
-        <f>ROUND(F171*G171,0)</f>
-        <v/>
-      </c>
-      <c r="I171" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J171" s="27">
-        <f>ROUND(H171*(1-I171),0)</f>
-        <v/>
-      </c>
-      <c r="K171" s="25">
-        <f>ROUND(J171*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L171" s="27">
-        <f>J171+K171</f>
-        <v/>
-      </c>
-      <c r="M171" s="8" t="n"/>
-      <c r="N171" s="8" t="n"/>
-      <c r="O171" s="22" t="n"/>
-      <c r="P171" s="8" t="n"/>
+      <c r="N171" s="19" t="n"/>
+      <c r="O171" s="19" t="n"/>
+      <c r="P171" s="19" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="22" t="n"/>
@@ -9136,7 +9135,7 @@
       <c r="C172" s="22" t="n"/>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Набор 9 конфет в брендированной коробке, партия 1 000</t>
+          <t xml:space="preserve">   Набор 9 конфет в брендированной коробке, партия 200</t>
         </is>
       </c>
       <c r="E172" s="22" t="inlineStr">
@@ -9145,7 +9144,7 @@
         </is>
       </c>
       <c r="F172" s="23" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G172" s="24">
         <f>Прайс!E127</f>
@@ -9176,182 +9175,182 @@
       <c r="P172" s="8" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="19" t="n"/>
-      <c r="B173" s="19" t="n"/>
-      <c r="C173" s="19" t="n"/>
-      <c r="D173" s="20" t="inlineStr">
+      <c r="A173" s="22" t="n"/>
+      <c r="B173" s="22" t="n"/>
+      <c r="C173" s="22" t="n"/>
+      <c r="D173" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Набор 9 конфет в брендированной коробке, партия 1 000</t>
+        </is>
+      </c>
+      <c r="E173" s="22" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F173" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G173" s="24">
+        <f>Прайс!E128</f>
+        <v/>
+      </c>
+      <c r="H173" s="25">
+        <f>ROUND(F173*G173,0)</f>
+        <v/>
+      </c>
+      <c r="I173" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="27">
+        <f>ROUND(H173*(1-I173),0)</f>
+        <v/>
+      </c>
+      <c r="K173" s="25">
+        <f>ROUND(J173*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L173" s="27">
+        <f>J173+K173</f>
+        <v/>
+      </c>
+      <c r="M173" s="8" t="n"/>
+      <c r="N173" s="8" t="n"/>
+      <c r="O173" s="22" t="n"/>
+      <c r="P173" s="8" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="19" t="n"/>
+      <c r="B174" s="19" t="n"/>
+      <c r="C174" s="19" t="n"/>
+      <c r="D174" s="20" t="inlineStr">
         <is>
           <t>Дегустационный набор</t>
         </is>
       </c>
-      <c r="E173" s="19" t="inlineStr">
+      <c r="E174" s="19" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="F173" s="31" t="n">
+      <c r="F174" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G173" s="32">
-        <f>Прайс!E128</f>
-        <v/>
-      </c>
-      <c r="H173" s="33">
-        <f>ROUND(F173*G173,0)</f>
-        <v/>
-      </c>
-      <c r="I173" s="34" t="n">
+      <c r="G174" s="32">
+        <f>Прайс!E129</f>
+        <v/>
+      </c>
+      <c r="H174" s="33">
+        <f>ROUND(F174*G174,0)</f>
+        <v/>
+      </c>
+      <c r="I174" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J173" s="35">
-        <f>ROUND(H173*(1-I173),0)</f>
-        <v/>
-      </c>
-      <c r="K173" s="33">
-        <f>ROUND(J173*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L173" s="35">
-        <f>J173+K173</f>
-        <v/>
-      </c>
-      <c r="M173" s="19" t="inlineStr">
+      <c r="J174" s="35">
+        <f>ROUND(H174*(1-I174),0)</f>
+        <v/>
+      </c>
+      <c r="K174" s="33">
+        <f>ROUND(J174*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L174" s="35">
+        <f>J174+K174</f>
+        <v/>
+      </c>
+      <c r="M174" s="19" t="inlineStr">
         <is>
           <t>5 р.д.</t>
         </is>
       </c>
-      <c r="N173" s="19" t="n"/>
-      <c r="O173" s="19" t="n"/>
-      <c r="P173" s="19" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="15" t="n">
+      <c r="N174" s="19" t="n"/>
+      <c r="O174" s="19" t="n"/>
+      <c r="P174" s="19" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="B174" s="16" t="inlineStr">
+      <c r="B175" s="16" t="inlineStr">
         <is>
           <t>Форма для сотрудников</t>
         </is>
       </c>
-      <c r="C174" s="17" t="inlineStr">
+      <c r="C175" s="17" t="inlineStr">
         <is>
           <t>Времена Года, Венеция</t>
         </is>
       </c>
-      <c r="D174" s="18" t="inlineStr">
+      <c r="D175" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E174" s="17" t="n"/>
-      <c r="F174" s="17" t="n"/>
-      <c r="G174" s="17" t="n"/>
-      <c r="H174" s="17" t="n"/>
-      <c r="I174" s="17" t="n"/>
-      <c r="J174" s="17" t="n"/>
-      <c r="K174" s="17" t="n"/>
-      <c r="L174" s="17" t="n"/>
-      <c r="M174" s="17" t="n"/>
-      <c r="N174" s="17">
+      <c r="E175" s="17" t="n"/>
+      <c r="F175" s="17" t="n"/>
+      <c r="G175" s="17" t="n"/>
+      <c r="H175" s="17" t="n"/>
+      <c r="I175" s="17" t="n"/>
+      <c r="J175" s="17" t="n"/>
+      <c r="K175" s="17" t="n"/>
+      <c r="L175" s="17" t="n"/>
+      <c r="M175" s="17" t="n"/>
+      <c r="N175" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$7,"0%")&amp;", остаток "&amp;TEXT(1-Прайс!$B$7,"0%")&amp;" после акта"</f>
         <v/>
       </c>
-      <c r="O174" s="17">
+      <c r="O175" s="17">
         <f>Прайс!$B$10&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P174" s="17" t="inlineStr">
+      <c r="P175" s="17" t="inlineStr">
         <is>
           <t>Индивидуальные мерки по запросу. Ткань и цвет утверждаем на образце. Гарантия 6 месяцев на швы и фурнитуру.</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="19" t="n"/>
-      <c r="B175" s="19" t="n"/>
-      <c r="C175" s="19" t="n"/>
-      <c r="D175" s="20" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="19" t="n"/>
+      <c r="B176" s="19" t="n"/>
+      <c r="C176" s="19" t="n"/>
+      <c r="D176" s="20" t="inlineStr">
         <is>
           <t>Комплект на 30 сотрудников, размеры 42-58: поло, брюки, жилет, вышивка</t>
         </is>
       </c>
-      <c r="E175" s="9" t="inlineStr">
+      <c r="E176" s="9" t="inlineStr">
         <is>
           <t>итого</t>
         </is>
       </c>
-      <c r="F175" s="19" t="n"/>
-      <c r="G175" s="19" t="n"/>
-      <c r="H175" s="21">
-        <f>SUM(H176:H179)</f>
-        <v/>
-      </c>
-      <c r="I175" s="19" t="n"/>
-      <c r="J175" s="21">
-        <f>SUM(J176:J179)</f>
-        <v/>
-      </c>
-      <c r="K175" s="21">
-        <f>SUM(K176:K179)</f>
-        <v/>
-      </c>
-      <c r="L175" s="21">
-        <f>SUM(L176:L179)</f>
-        <v/>
-      </c>
-      <c r="M175" s="19" t="inlineStr">
+      <c r="F176" s="19" t="n"/>
+      <c r="G176" s="19" t="n"/>
+      <c r="H176" s="21">
+        <f>SUM(H177:H180)</f>
+        <v/>
+      </c>
+      <c r="I176" s="19" t="n"/>
+      <c r="J176" s="21">
+        <f>SUM(J177:J180)</f>
+        <v/>
+      </c>
+      <c r="K176" s="21">
+        <f>SUM(K177:K180)</f>
+        <v/>
+      </c>
+      <c r="L176" s="21">
+        <f>SUM(L177:L180)</f>
+        <v/>
+      </c>
+      <c r="M176" s="19" t="inlineStr">
         <is>
           <t>25 р.д. после утверждения образца</t>
         </is>
       </c>
-      <c r="N175" s="19" t="n"/>
-      <c r="O175" s="19" t="n"/>
-      <c r="P175" s="19" t="n"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="22" t="n"/>
-      <c r="B176" s="22" t="n"/>
-      <c r="C176" s="22" t="n"/>
-      <c r="D176" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Поло или рубашка, хлопок с эластаном</t>
-        </is>
-      </c>
-      <c r="E176" s="22" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F176" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="G176" s="24">
-        <f>Прайс!E130</f>
-        <v/>
-      </c>
-      <c r="H176" s="25">
-        <f>ROUND(F176*G176,0)</f>
-        <v/>
-      </c>
-      <c r="I176" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J176" s="27">
-        <f>ROUND(H176*(1-I176),0)</f>
-        <v/>
-      </c>
-      <c r="K176" s="25">
-        <f>ROUND(J176*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L176" s="27">
-        <f>J176+K176</f>
-        <v/>
-      </c>
-      <c r="M176" s="8" t="n"/>
-      <c r="N176" s="8" t="n"/>
-      <c r="O176" s="22" t="n"/>
-      <c r="P176" s="8" t="n"/>
+      <c r="N176" s="19" t="n"/>
+      <c r="O176" s="19" t="n"/>
+      <c r="P176" s="19" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="22" t="n"/>
@@ -9359,7 +9358,7 @@
       <c r="C177" s="22" t="n"/>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Брюки, костюмная ткань</t>
+          <t xml:space="preserve">   Поло или рубашка, хлопок с эластаном</t>
         </is>
       </c>
       <c r="E177" s="22" t="inlineStr">
@@ -9404,7 +9403,7 @@
       <c r="C178" s="22" t="n"/>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Жилет, костюмная ткань, подкладка</t>
+          <t xml:space="preserve">   Брюки, костюмная ткань</t>
         </is>
       </c>
       <c r="E178" s="22" t="inlineStr">
@@ -9449,7 +9448,7 @@
       <c r="C179" s="22" t="n"/>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Вышивка логотипа на груди</t>
+          <t xml:space="preserve">   Жилет, костюмная ткань, подкладка</t>
         </is>
       </c>
       <c r="E179" s="22" t="inlineStr">
@@ -9458,7 +9457,7 @@
         </is>
       </c>
       <c r="F179" s="23" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G179" s="24">
         <f>Прайс!E133</f>
@@ -9486,60 +9485,56 @@
       <c r="M179" s="8" t="n"/>
       <c r="N179" s="8" t="n"/>
       <c r="O179" s="22" t="n"/>
-      <c r="P179" s="8" t="inlineStr">
+      <c r="P179" s="8" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="22" t="n"/>
+      <c r="B180" s="22" t="n"/>
+      <c r="C180" s="22" t="n"/>
+      <c r="D180" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Вышивка логотипа на груди</t>
+        </is>
+      </c>
+      <c r="E180" s="22" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F180" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="G180" s="24">
+        <f>Прайс!E134</f>
+        <v/>
+      </c>
+      <c r="H180" s="25">
+        <f>ROUND(F180*G180,0)</f>
+        <v/>
+      </c>
+      <c r="I180" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="27">
+        <f>ROUND(H180*(1-I180),0)</f>
+        <v/>
+      </c>
+      <c r="K180" s="25">
+        <f>ROUND(J180*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L180" s="27">
+        <f>J180+K180</f>
+        <v/>
+      </c>
+      <c r="M180" s="8" t="n"/>
+      <c r="N180" s="8" t="n"/>
+      <c r="O180" s="22" t="n"/>
+      <c r="P180" s="8" t="inlineStr">
         <is>
           <t>поло и жилет</t>
         </is>
       </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="19" t="n"/>
-      <c r="B180" s="19" t="n"/>
-      <c r="C180" s="19" t="n"/>
-      <c r="D180" s="20" t="inlineStr">
-        <is>
-          <t>Образец комплекта</t>
-        </is>
-      </c>
-      <c r="E180" s="19" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="F180" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G180" s="32">
-        <f>Прайс!E134</f>
-        <v/>
-      </c>
-      <c r="H180" s="33">
-        <f>ROUND(F180*G180,0)</f>
-        <v/>
-      </c>
-      <c r="I180" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J180" s="35">
-        <f>ROUND(H180*(1-I180),0)</f>
-        <v/>
-      </c>
-      <c r="K180" s="33">
-        <f>ROUND(J180*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L180" s="35">
-        <f>J180+K180</f>
-        <v/>
-      </c>
-      <c r="M180" s="19" t="inlineStr">
-        <is>
-          <t>10 р.д.</t>
-        </is>
-      </c>
-      <c r="N180" s="19" t="n"/>
-      <c r="O180" s="19" t="n"/>
-      <c r="P180" s="19" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="19" t="n"/>
@@ -9547,7 +9542,7 @@
       <c r="C181" s="19" t="n"/>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>Дошив 1-5 комплектов в течение года</t>
+          <t>Образец комплекта</t>
         </is>
       </c>
       <c r="E181" s="19" t="inlineStr">
@@ -9583,7 +9578,7 @@
       </c>
       <c r="M181" s="19" t="inlineStr">
         <is>
-          <t>15 р.д.</t>
+          <t>10 р.д.</t>
         </is>
       </c>
       <c r="N181" s="19" t="n"/>
@@ -9591,133 +9586,137 @@
       <c r="P181" s="19" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="15" t="n">
+      <c r="A182" s="19" t="n"/>
+      <c r="B182" s="19" t="n"/>
+      <c r="C182" s="19" t="n"/>
+      <c r="D182" s="20" t="inlineStr">
+        <is>
+          <t>Дошив 1-5 комплектов в течение года</t>
+        </is>
+      </c>
+      <c r="E182" s="19" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="F182" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="32">
+        <f>Прайс!E136</f>
+        <v/>
+      </c>
+      <c r="H182" s="33">
+        <f>ROUND(F182*G182,0)</f>
+        <v/>
+      </c>
+      <c r="I182" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" s="35">
+        <f>ROUND(H182*(1-I182),0)</f>
+        <v/>
+      </c>
+      <c r="K182" s="33">
+        <f>ROUND(J182*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L182" s="35">
+        <f>J182+K182</f>
+        <v/>
+      </c>
+      <c r="M182" s="19" t="inlineStr">
+        <is>
+          <t>15 р.д.</t>
+        </is>
+      </c>
+      <c r="N182" s="19" t="n"/>
+      <c r="O182" s="19" t="n"/>
+      <c r="P182" s="19" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="B182" s="16" t="inlineStr">
+      <c r="B183" s="16" t="inlineStr">
         <is>
           <t>Агентство по организации мероприятий</t>
         </is>
       </c>
-      <c r="C182" s="17" t="inlineStr">
+      <c r="C183" s="17" t="inlineStr">
         <is>
           <t>Времена Года, ЦДМ, Венеция</t>
         </is>
       </c>
-      <c r="D182" s="18" t="inlineStr">
+      <c r="D183" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E182" s="17" t="n"/>
-      <c r="F182" s="17" t="n"/>
-      <c r="G182" s="17" t="n"/>
-      <c r="H182" s="17" t="n"/>
-      <c r="I182" s="17" t="n"/>
-      <c r="J182" s="17" t="n"/>
-      <c r="K182" s="17" t="n"/>
-      <c r="L182" s="17" t="n"/>
-      <c r="M182" s="17" t="n"/>
-      <c r="N182" s="17">
+      <c r="E183" s="17" t="n"/>
+      <c r="F183" s="17" t="n"/>
+      <c r="G183" s="17" t="n"/>
+      <c r="H183" s="17" t="n"/>
+      <c r="I183" s="17" t="n"/>
+      <c r="J183" s="17" t="n"/>
+      <c r="K183" s="17" t="n"/>
+      <c r="L183" s="17" t="n"/>
+      <c r="M183" s="17" t="n"/>
+      <c r="N183" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$7,"0%")&amp;", остаток "&amp;TEXT(1-Прайс!$B$7,"0%")&amp;" после акта"</f>
         <v/>
       </c>
-      <c r="O182" s="17">
+      <c r="O183" s="17">
         <f>Прайс!$B$10&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P182" s="17" t="inlineStr">
+      <c r="P183" s="17" t="inlineStr">
         <is>
           <t>Концепция бесплатно. Выделенный менеджер на проект. Агентская комиссия указана отдельной строкой. Минимальный срок подготовки: 40 гостей 10 р.д., 100 гостей 15 р.д.</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="19" t="n"/>
-      <c r="B183" s="19" t="n"/>
-      <c r="C183" s="19" t="n"/>
-      <c r="D183" s="20" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="19" t="n"/>
+      <c r="B184" s="19" t="n"/>
+      <c r="C184" s="19" t="n"/>
+      <c r="D184" s="20" t="inlineStr">
         <is>
           <t>Пресс-завтрак к открытию сезона: 40 гостей, 2,5 ч, атриум, будний день</t>
         </is>
       </c>
-      <c r="E183" s="9" t="inlineStr">
+      <c r="E184" s="9" t="inlineStr">
         <is>
           <t>итого</t>
         </is>
       </c>
-      <c r="F183" s="19" t="n"/>
-      <c r="G183" s="19" t="n"/>
-      <c r="H183" s="21">
-        <f>SUM(H184:H192)</f>
-        <v/>
-      </c>
-      <c r="I183" s="19" t="n"/>
-      <c r="J183" s="21">
-        <f>SUM(J184:J192)</f>
-        <v/>
-      </c>
-      <c r="K183" s="21">
-        <f>SUM(K184:K192)</f>
-        <v/>
-      </c>
-      <c r="L183" s="21">
-        <f>SUM(L184:L192)</f>
-        <v/>
-      </c>
-      <c r="M183" s="19" t="inlineStr">
+      <c r="F184" s="19" t="n"/>
+      <c r="G184" s="19" t="n"/>
+      <c r="H184" s="21">
+        <f>SUM(H185:H193)</f>
+        <v/>
+      </c>
+      <c r="I184" s="19" t="n"/>
+      <c r="J184" s="21">
+        <f>SUM(J185:J193)</f>
+        <v/>
+      </c>
+      <c r="K184" s="21">
+        <f>SUM(K185:K193)</f>
+        <v/>
+      </c>
+      <c r="L184" s="21">
+        <f>SUM(L185:L193)</f>
+        <v/>
+      </c>
+      <c r="M184" s="19" t="inlineStr">
         <is>
           <t>10 р.д. от утверждения концепции</t>
         </is>
       </c>
-      <c r="N183" s="19" t="n"/>
-      <c r="O183" s="19" t="n"/>
-      <c r="P183" s="19" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="22" t="n"/>
-      <c r="B184" s="22" t="n"/>
-      <c r="C184" s="22" t="n"/>
-      <c r="D184" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Декор зоны пресс-завтрака</t>
-        </is>
-      </c>
-      <c r="E184" s="22" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="F184" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G184" s="24">
-        <f>Прайс!E136</f>
-        <v/>
-      </c>
-      <c r="H184" s="25">
-        <f>ROUND(F184*G184,0)</f>
-        <v/>
-      </c>
-      <c r="I184" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J184" s="27">
-        <f>ROUND(H184*(1-I184),0)</f>
-        <v/>
-      </c>
-      <c r="K184" s="25">
-        <f>ROUND(J184*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L184" s="27">
-        <f>J184+K184</f>
-        <v/>
-      </c>
-      <c r="M184" s="8" t="n"/>
-      <c r="N184" s="8" t="n"/>
-      <c r="O184" s="22" t="n"/>
-      <c r="P184" s="8" t="n"/>
+      <c r="N184" s="19" t="n"/>
+      <c r="O184" s="19" t="n"/>
+      <c r="P184" s="19" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="22" t="n"/>
@@ -9725,16 +9724,16 @@
       <c r="C185" s="22" t="n"/>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Кейтеринг: завтрак-фуршет, кофе-брейк, посуда, официанты</t>
+          <t xml:space="preserve">   Декор зоны пресс-завтрака</t>
         </is>
       </c>
       <c r="E185" s="22" t="inlineStr">
         <is>
-          <t>гость</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="F185" s="23" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G185" s="24">
         <f>Прайс!E137</f>
@@ -9770,16 +9769,16 @@
       <c r="C186" s="22" t="n"/>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Звук: акустика, 2 радиомикрофона, техник</t>
+          <t xml:space="preserve">   Кейтеринг: завтрак-фуршет, кофе-брейк, посуда, официанты</t>
         </is>
       </c>
       <c r="E186" s="22" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>гость</t>
         </is>
       </c>
       <c r="F186" s="23" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G186" s="24">
         <f>Прайс!E138</f>
@@ -9815,12 +9814,12 @@
       <c r="C187" s="22" t="n"/>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ведущий</t>
+          <t xml:space="preserve">   Звук: акустика, 2 радиомикрофона, техник</t>
         </is>
       </c>
       <c r="E187" s="22" t="inlineStr">
         <is>
-          <t>мероприятие</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="F187" s="23" t="n">
@@ -9860,12 +9859,12 @@
       <c r="C188" s="22" t="n"/>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Фотосъемка, 3 ч</t>
+          <t xml:space="preserve">   Ведущий</t>
         </is>
       </c>
       <c r="E188" s="22" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>мероприятие</t>
         </is>
       </c>
       <c r="F188" s="23" t="n">
@@ -9905,7 +9904,7 @@
       <c r="C189" s="22" t="n"/>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Видеосъемка и отчетный ролик</t>
+          <t xml:space="preserve">   Фотосъемка, 3 ч</t>
         </is>
       </c>
       <c r="E189" s="22" t="inlineStr">
@@ -9950,16 +9949,16 @@
       <c r="C190" s="22" t="n"/>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Welcome-подарок гостю</t>
+          <t xml:space="preserve">   Видеосъемка и отчетный ролик</t>
         </is>
       </c>
       <c r="E190" s="22" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="F190" s="23" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G190" s="24">
         <f>Прайс!E142</f>
@@ -9995,16 +9994,16 @@
       <c r="C191" s="22" t="n"/>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Персонал и координация на площадке</t>
+          <t xml:space="preserve">   Welcome-подарок гостю</t>
         </is>
       </c>
       <c r="E191" s="22" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="F191" s="23" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G191" s="24">
         <f>Прайс!E143</f>
@@ -10035,40 +10034,38 @@
       <c r="P191" s="8" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="29" t="n"/>
-      <c r="B192" s="29" t="n"/>
-      <c r="C192" s="29" t="n"/>
-      <c r="D192" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Агентская комиссия</t>
-        </is>
-      </c>
-      <c r="E192" s="29" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F192" s="26">
-        <f>Прайс!$B$14</f>
-        <v/>
-      </c>
-      <c r="G192" s="37">
-        <f>SUM(H184:H191)</f>
-        <v/>
-      </c>
-      <c r="H192" s="37">
+      <c r="A192" s="22" t="n"/>
+      <c r="B192" s="22" t="n"/>
+      <c r="C192" s="22" t="n"/>
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Персонал и координация на площадке</t>
+        </is>
+      </c>
+      <c r="E192" s="22" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="F192" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="24">
+        <f>Прайс!E144</f>
+        <v/>
+      </c>
+      <c r="H192" s="25">
         <f>ROUND(F192*G192,0)</f>
         <v/>
       </c>
-      <c r="I192" s="26">
-        <f>Прайс!$B$6</f>
-        <v/>
+      <c r="I192" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="J192" s="27">
         <f>ROUND(H192*(1-I192),0)</f>
         <v/>
       </c>
-      <c r="K192" s="37">
+      <c r="K192" s="25">
         <f>ROUND(J192*Прайс!$B$5,0)</f>
         <v/>
       </c>
@@ -10076,106 +10073,103 @@
         <f>J192+K192</f>
         <v/>
       </c>
-      <c r="M192" s="29" t="n"/>
-      <c r="N192" s="29" t="n"/>
-      <c r="O192" s="29" t="n"/>
-      <c r="P192" s="19" t="inlineStr">
+      <c r="M192" s="8" t="n"/>
+      <c r="N192" s="8" t="n"/>
+      <c r="O192" s="22" t="n"/>
+      <c r="P192" s="8" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="29" t="n"/>
+      <c r="B193" s="29" t="n"/>
+      <c r="C193" s="29" t="n"/>
+      <c r="D193" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Агентская комиссия</t>
+        </is>
+      </c>
+      <c r="E193" s="29" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F193" s="26">
+        <f>Прайс!$B$14</f>
+        <v/>
+      </c>
+      <c r="G193" s="37">
+        <f>SUM(H185:H192)</f>
+        <v/>
+      </c>
+      <c r="H193" s="37">
+        <f>ROUND(F193*G193,0)</f>
+        <v/>
+      </c>
+      <c r="I193" s="26">
+        <f>Прайс!$B$6</f>
+        <v/>
+      </c>
+      <c r="J193" s="27">
+        <f>ROUND(H193*(1-I193),0)</f>
+        <v/>
+      </c>
+      <c r="K193" s="37">
+        <f>ROUND(J193*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L193" s="27">
+        <f>J193+K193</f>
+        <v/>
+      </c>
+      <c r="M193" s="29" t="n"/>
+      <c r="N193" s="29" t="n"/>
+      <c r="O193" s="29" t="n"/>
+      <c r="P193" s="19" t="inlineStr">
         <is>
           <t>От суммы сметы, указана отдельно по запросу ТЗ</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="15" t="n">
+    <row r="194">
+      <c r="A194" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="B193" s="16" t="inlineStr">
+      <c r="B194" s="16" t="inlineStr">
         <is>
           <t>Декорирование, флористика</t>
         </is>
       </c>
-      <c r="C193" s="17" t="inlineStr">
+      <c r="C194" s="17" t="inlineStr">
         <is>
           <t>Времена Года, ЦДМ, Венеция</t>
         </is>
       </c>
-      <c r="D193" s="18" t="inlineStr">
+      <c r="D194" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E193" s="17" t="n"/>
-      <c r="F193" s="17" t="n"/>
-      <c r="G193" s="17" t="n"/>
-      <c r="H193" s="17" t="n"/>
-      <c r="I193" s="17" t="n"/>
-      <c r="J193" s="17" t="n"/>
-      <c r="K193" s="17" t="n"/>
-      <c r="L193" s="17" t="n"/>
-      <c r="M193" s="17" t="n"/>
-      <c r="N193" s="17">
+      <c r="E194" s="17" t="n"/>
+      <c r="F194" s="17" t="n"/>
+      <c r="G194" s="17" t="n"/>
+      <c r="H194" s="17" t="n"/>
+      <c r="I194" s="17" t="n"/>
+      <c r="J194" s="17" t="n"/>
+      <c r="K194" s="17" t="n"/>
+      <c r="L194" s="17" t="n"/>
+      <c r="M194" s="17" t="n"/>
+      <c r="N194" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$7,"0%")&amp;", остаток "&amp;TEXT(1-Прайс!$B$7,"0%")&amp;" после акта"</f>
         <v/>
       </c>
-      <c r="O193" s="17">
+      <c r="O194" s="17">
         <f>Прайс!$B$10&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P193" s="17" t="inlineStr">
+      <c r="P194" s="17" t="inlineStr">
         <is>
           <t>Производство атриума считаем по утвержденному эскизу: размеры, материалы и свет задают смету. Эскиз или 3D-визуализация до старта производства. Материалы с сертификатами пожарной безопасности. Монтаж и демонтаж своими силами, ночью.</t>
         </is>
       </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="19" t="n"/>
-      <c r="B194" s="19" t="n"/>
-      <c r="C194" s="19" t="n"/>
-      <c r="D194" s="20" t="inlineStr">
-        <is>
-          <t>(1а) Эскиз и 3D-визуализация оформления атриума</t>
-        </is>
-      </c>
-      <c r="E194" s="19" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="F194" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G194" s="32">
-        <f>Прайс!E144</f>
-        <v/>
-      </c>
-      <c r="H194" s="33">
-        <f>ROUND(F194*G194,0)</f>
-        <v/>
-      </c>
-      <c r="I194" s="34">
-        <f>Прайс!$B$6</f>
-        <v/>
-      </c>
-      <c r="J194" s="35">
-        <f>ROUND(H194*(1-I194),0)</f>
-        <v/>
-      </c>
-      <c r="K194" s="33">
-        <f>ROUND(J194*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L194" s="35">
-        <f>J194+K194</f>
-        <v/>
-      </c>
-      <c r="M194" s="19" t="inlineStr">
-        <is>
-          <t>5 р.д.</t>
-        </is>
-      </c>
-      <c r="N194" s="19" t="n"/>
-      <c r="O194" s="19" t="n"/>
-      <c r="P194" s="19" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="19" t="n"/>
@@ -10183,20 +10177,44 @@
       <c r="C195" s="19" t="n"/>
       <c r="D195" s="20" t="inlineStr">
         <is>
-          <t>(1б) Производство и монтаж: композиция до 6 м + 4 фотозоны</t>
-        </is>
-      </c>
-      <c r="E195" s="19" t="n"/>
-      <c r="F195" s="19" t="n"/>
-      <c r="G195" s="19" t="n"/>
-      <c r="H195" s="19" t="n"/>
-      <c r="I195" s="19" t="n"/>
-      <c r="J195" s="19" t="n"/>
-      <c r="K195" s="19" t="n"/>
-      <c r="L195" s="19" t="n"/>
+          <t>(1а) Эскиз и 3D-визуализация оформления атриума</t>
+        </is>
+      </c>
+      <c r="E195" s="19" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="F195" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="32">
+        <f>Прайс!E145</f>
+        <v/>
+      </c>
+      <c r="H195" s="33">
+        <f>ROUND(F195*G195,0)</f>
+        <v/>
+      </c>
+      <c r="I195" s="34">
+        <f>Прайс!$B$6</f>
+        <v/>
+      </c>
+      <c r="J195" s="35">
+        <f>ROUND(H195*(1-I195),0)</f>
+        <v/>
+      </c>
+      <c r="K195" s="33">
+        <f>ROUND(J195*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L195" s="35">
+        <f>J195+K195</f>
+        <v/>
+      </c>
       <c r="M195" s="19" t="inlineStr">
         <is>
-          <t>Расчет за 3 р.д. после утверждения эскиза</t>
+          <t>5 р.д.</t>
         </is>
       </c>
       <c r="N195" s="19" t="n"/>
@@ -10204,44 +10222,30 @@
       <c r="P195" s="19" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="22" t="n"/>
-      <c r="B196" s="22" t="n"/>
-      <c r="C196" s="22" t="n"/>
-      <c r="D196" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Центральная композиция высотой до 6 м, производство</t>
-        </is>
-      </c>
-      <c r="E196" s="22" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F196" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="H196" s="22" t="n"/>
-      <c r="I196" s="29" t="n"/>
-      <c r="J196" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="K196" s="22" t="n"/>
-      <c r="L196" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="M196" s="8" t="n"/>
-      <c r="N196" s="8" t="n"/>
-      <c r="O196" s="22" t="n"/>
-      <c r="P196" s="8" t="n"/>
+      <c r="A196" s="19" t="n"/>
+      <c r="B196" s="19" t="n"/>
+      <c r="C196" s="19" t="n"/>
+      <c r="D196" s="20" t="inlineStr">
+        <is>
+          <t>(1б) Производство и монтаж: композиция до 6 м + 4 фотозоны</t>
+        </is>
+      </c>
+      <c r="E196" s="19" t="n"/>
+      <c r="F196" s="19" t="n"/>
+      <c r="G196" s="19" t="n"/>
+      <c r="H196" s="19" t="n"/>
+      <c r="I196" s="19" t="n"/>
+      <c r="J196" s="19" t="n"/>
+      <c r="K196" s="19" t="n"/>
+      <c r="L196" s="19" t="n"/>
+      <c r="M196" s="19" t="inlineStr">
+        <is>
+          <t>Расчет за 3 р.д. после утверждения эскиза</t>
+        </is>
+      </c>
+      <c r="N196" s="19" t="n"/>
+      <c r="O196" s="19" t="n"/>
+      <c r="P196" s="19" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="22" t="n"/>
@@ -10249,7 +10253,7 @@
       <c r="C197" s="22" t="n"/>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Малая фотозона, производство</t>
+          <t xml:space="preserve">   Центральная композиция высотой до 6 м, производство</t>
         </is>
       </c>
       <c r="E197" s="22" t="inlineStr">
@@ -10258,7 +10262,7 @@
         </is>
       </c>
       <c r="F197" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G197" s="28" t="inlineStr">
         <is>
@@ -10289,16 +10293,16 @@
       <c r="C198" s="22" t="n"/>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Монтаж и демонтаж в ночное время</t>
+          <t xml:space="preserve">   Малая фотозона, производство</t>
         </is>
       </c>
       <c r="E198" s="22" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="F198" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G198" s="28" t="inlineStr">
         <is>
@@ -10324,52 +10328,44 @@
       <c r="P198" s="8" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="19" t="n"/>
-      <c r="B199" s="19" t="n"/>
-      <c r="C199" s="19" t="n"/>
-      <c r="D199" s="20" t="inlineStr">
-        <is>
-          <t>Хранение между сезонами</t>
-        </is>
-      </c>
-      <c r="E199" s="19" t="inlineStr">
-        <is>
-          <t>мес.</t>
-        </is>
-      </c>
-      <c r="F199" s="31" t="n">
+      <c r="A199" s="22" t="n"/>
+      <c r="B199" s="22" t="n"/>
+      <c r="C199" s="22" t="n"/>
+      <c r="D199" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Монтаж и демонтаж в ночное время</t>
+        </is>
+      </c>
+      <c r="E199" s="22" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="F199" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G199" s="36" t="inlineStr">
+      <c r="G199" s="28" t="inlineStr">
         <is>
           <t>По запросу</t>
         </is>
       </c>
-      <c r="H199" s="19" t="n"/>
-      <c r="I199" s="19" t="n"/>
-      <c r="J199" s="36" t="inlineStr">
+      <c r="H199" s="22" t="n"/>
+      <c r="I199" s="29" t="n"/>
+      <c r="J199" s="28" t="inlineStr">
         <is>
           <t>По запросу</t>
         </is>
       </c>
-      <c r="K199" s="19" t="n"/>
-      <c r="L199" s="36" t="inlineStr">
+      <c r="K199" s="22" t="n"/>
+      <c r="L199" s="28" t="inlineStr">
         <is>
           <t>По запросу</t>
         </is>
       </c>
-      <c r="M199" s="19" t="inlineStr">
-        <is>
-          <t>По объему декора</t>
-        </is>
-      </c>
-      <c r="N199" s="19" t="n"/>
-      <c r="O199" s="19" t="n"/>
-      <c r="P199" s="19" t="inlineStr">
-        <is>
-          <t>за месяц</t>
-        </is>
-      </c>
+      <c r="M199" s="8" t="n"/>
+      <c r="N199" s="8" t="n"/>
+      <c r="O199" s="22" t="n"/>
+      <c r="P199" s="8" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="19" t="n"/>
@@ -10377,86 +10373,89 @@
       <c r="C200" s="19" t="n"/>
       <c r="D200" s="20" t="inlineStr">
         <is>
-          <t>(2) Флористика мероприятия на 40 гостей: 5 столов и фотозона</t>
-        </is>
-      </c>
-      <c r="E200" s="9" t="inlineStr">
-        <is>
-          <t>итого</t>
-        </is>
-      </c>
-      <c r="F200" s="19" t="n"/>
-      <c r="G200" s="19" t="n"/>
-      <c r="H200" s="21">
-        <f>SUM(H201:H203)</f>
-        <v/>
-      </c>
+          <t>Хранение между сезонами</t>
+        </is>
+      </c>
+      <c r="E200" s="19" t="inlineStr">
+        <is>
+          <t>мес.</t>
+        </is>
+      </c>
+      <c r="F200" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="36" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="H200" s="19" t="n"/>
       <c r="I200" s="19" t="n"/>
-      <c r="J200" s="21">
-        <f>SUM(J201:J203)</f>
-        <v/>
-      </c>
-      <c r="K200" s="21">
-        <f>SUM(K201:K203)</f>
-        <v/>
-      </c>
-      <c r="L200" s="21">
-        <f>SUM(L201:L203)</f>
-        <v/>
+      <c r="J200" s="36" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="K200" s="19" t="n"/>
+      <c r="L200" s="36" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
       </c>
       <c r="M200" s="19" t="inlineStr">
         <is>
-          <t>Монтаж в день мероприятия</t>
+          <t>По объему декора</t>
         </is>
       </c>
       <c r="N200" s="19" t="n"/>
       <c r="O200" s="19" t="n"/>
-      <c r="P200" s="19" t="n"/>
+      <c r="P200" s="19" t="inlineStr">
+        <is>
+          <t>за месяц</t>
+        </is>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="22" t="n"/>
-      <c r="B201" s="22" t="n"/>
-      <c r="C201" s="22" t="n"/>
-      <c r="D201" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Флористическая композиция на стол</t>
-        </is>
-      </c>
-      <c r="E201" s="22" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F201" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G201" s="24">
-        <f>Прайс!E149</f>
-        <v/>
-      </c>
-      <c r="H201" s="25">
-        <f>ROUND(F201*G201,0)</f>
-        <v/>
-      </c>
-      <c r="I201" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" s="27">
-        <f>ROUND(H201*(1-I201),0)</f>
-        <v/>
-      </c>
-      <c r="K201" s="25">
-        <f>ROUND(J201*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L201" s="27">
-        <f>J201+K201</f>
-        <v/>
-      </c>
-      <c r="M201" s="8" t="n"/>
-      <c r="N201" s="8" t="n"/>
-      <c r="O201" s="22" t="n"/>
-      <c r="P201" s="8" t="n"/>
+      <c r="A201" s="19" t="n"/>
+      <c r="B201" s="19" t="n"/>
+      <c r="C201" s="19" t="n"/>
+      <c r="D201" s="20" t="inlineStr">
+        <is>
+          <t>(2) Флористика мероприятия на 40 гостей: 5 столов и фотозона</t>
+        </is>
+      </c>
+      <c r="E201" s="9" t="inlineStr">
+        <is>
+          <t>итого</t>
+        </is>
+      </c>
+      <c r="F201" s="19" t="n"/>
+      <c r="G201" s="19" t="n"/>
+      <c r="H201" s="21">
+        <f>SUM(H202:H204)</f>
+        <v/>
+      </c>
+      <c r="I201" s="19" t="n"/>
+      <c r="J201" s="21">
+        <f>SUM(J202:J204)</f>
+        <v/>
+      </c>
+      <c r="K201" s="21">
+        <f>SUM(K202:K204)</f>
+        <v/>
+      </c>
+      <c r="L201" s="21">
+        <f>SUM(L202:L204)</f>
+        <v/>
+      </c>
+      <c r="M201" s="19" t="inlineStr">
+        <is>
+          <t>Монтаж в день мероприятия</t>
+        </is>
+      </c>
+      <c r="N201" s="19" t="n"/>
+      <c r="O201" s="19" t="n"/>
+      <c r="P201" s="19" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="22" t="n"/>
@@ -10464,7 +10463,7 @@
       <c r="C202" s="22" t="n"/>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Флористическая фотозона</t>
+          <t xml:space="preserve">   Флористическая композиция на стол</t>
         </is>
       </c>
       <c r="E202" s="22" t="inlineStr">
@@ -10473,7 +10472,7 @@
         </is>
       </c>
       <c r="F202" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G202" s="24">
         <f>Прайс!E150</f>
@@ -10509,12 +10508,12 @@
       <c r="C203" s="22" t="n"/>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Доставка, монтаж и демонтаж флористики</t>
+          <t xml:space="preserve">   Флористическая фотозона</t>
         </is>
       </c>
       <c r="E203" s="22" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="F203" s="23" t="n">
@@ -10549,265 +10548,265 @@
       <c r="P203" s="8" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="15" t="n">
+      <c r="A204" s="22" t="n"/>
+      <c r="B204" s="22" t="n"/>
+      <c r="C204" s="22" t="n"/>
+      <c r="D204" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Доставка, монтаж и демонтаж флористики</t>
+        </is>
+      </c>
+      <c r="E204" s="22" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="F204" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="24">
+        <f>Прайс!E152</f>
+        <v/>
+      </c>
+      <c r="H204" s="25">
+        <f>ROUND(F204*G204,0)</f>
+        <v/>
+      </c>
+      <c r="I204" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="27">
+        <f>ROUND(H204*(1-I204),0)</f>
+        <v/>
+      </c>
+      <c r="K204" s="25">
+        <f>ROUND(J204*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L204" s="27">
+        <f>J204+K204</f>
+        <v/>
+      </c>
+      <c r="M204" s="8" t="n"/>
+      <c r="N204" s="8" t="n"/>
+      <c r="O204" s="22" t="n"/>
+      <c r="P204" s="8" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="B204" s="16" t="inlineStr">
+      <c r="B205" s="16" t="inlineStr">
         <is>
           <t>Кейтеринг</t>
         </is>
       </c>
-      <c r="C204" s="17" t="inlineStr">
+      <c r="C205" s="17" t="inlineStr">
         <is>
           <t>Времена Года, Венеция</t>
         </is>
       </c>
-      <c r="D204" s="18" t="inlineStr">
+      <c r="D205" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E204" s="17" t="n"/>
-      <c r="F204" s="17" t="n"/>
-      <c r="G204" s="17" t="n"/>
-      <c r="H204" s="17" t="n"/>
-      <c r="I204" s="17" t="n"/>
-      <c r="J204" s="17" t="n"/>
-      <c r="K204" s="17" t="n"/>
-      <c r="L204" s="17" t="n"/>
-      <c r="M204" s="17" t="n"/>
-      <c r="N204" s="17">
+      <c r="E205" s="17" t="n"/>
+      <c r="F205" s="17" t="n"/>
+      <c r="G205" s="17" t="n"/>
+      <c r="H205" s="17" t="n"/>
+      <c r="I205" s="17" t="n"/>
+      <c r="J205" s="17" t="n"/>
+      <c r="K205" s="17" t="n"/>
+      <c r="L205" s="17" t="n"/>
+      <c r="M205" s="17" t="n"/>
+      <c r="N205" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$7,"0%")&amp;", остаток "&amp;TEXT(1-Прайс!$B$7,"0%")&amp;" после акта"</f>
         <v/>
       </c>
-      <c r="O204" s="17">
+      <c r="O205" s="17">
         <f>Прайс!$B$10&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P204" s="17" t="inlineStr">
+      <c r="P205" s="17" t="inlineStr">
         <is>
           <t>Минимум 30 гостей. Посуда, текстиль, официанты, доставка, сервировка и уборка входят в цену на персону. Вегетарианское, безглютеновое и детское меню делаем. Персонал с медкнижками.</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="19" t="n"/>
-      <c r="B205" s="19" t="n"/>
-      <c r="C205" s="19" t="n"/>
-      <c r="D205" s="20" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="19" t="n"/>
+      <c r="B206" s="19" t="n"/>
+      <c r="C206" s="19" t="n"/>
+      <c r="D206" s="20" t="inlineStr">
         <is>
           <t>(1) Завтрак-фуршет на 40 гостей, 2,5 ч, кофе-брейк</t>
         </is>
       </c>
-      <c r="E205" s="9" t="inlineStr">
+      <c r="E206" s="9" t="inlineStr">
         <is>
           <t>итого</t>
         </is>
       </c>
-      <c r="F205" s="19" t="n"/>
-      <c r="G205" s="19" t="n"/>
-      <c r="H205" s="21">
-        <f>SUM(H206:H206)</f>
-        <v/>
-      </c>
-      <c r="I205" s="19" t="n"/>
-      <c r="J205" s="21">
-        <f>SUM(J206:J206)</f>
-        <v/>
-      </c>
-      <c r="K205" s="21">
-        <f>SUM(K206:K206)</f>
-        <v/>
-      </c>
-      <c r="L205" s="21">
-        <f>SUM(L206:L206)</f>
-        <v/>
-      </c>
-      <c r="M205" s="19" t="inlineStr">
+      <c r="F206" s="19" t="n"/>
+      <c r="G206" s="19" t="n"/>
+      <c r="H206" s="21">
+        <f>SUM(H207:H207)</f>
+        <v/>
+      </c>
+      <c r="I206" s="19" t="n"/>
+      <c r="J206" s="21">
+        <f>SUM(J207:J207)</f>
+        <v/>
+      </c>
+      <c r="K206" s="21">
+        <f>SUM(K207:K207)</f>
+        <v/>
+      </c>
+      <c r="L206" s="21">
+        <f>SUM(L207:L207)</f>
+        <v/>
+      </c>
+      <c r="M206" s="19" t="inlineStr">
         <is>
           <t>Заказ за 5 р.д.</t>
         </is>
       </c>
-      <c r="N205" s="19" t="n"/>
-      <c r="O205" s="19" t="n"/>
-      <c r="P205" s="19" t="n"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="22" t="n"/>
-      <c r="B206" s="22" t="n"/>
-      <c r="C206" s="22" t="n"/>
-      <c r="D206" s="8" t="inlineStr">
+      <c r="N206" s="19" t="n"/>
+      <c r="O206" s="19" t="n"/>
+      <c r="P206" s="19" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="22" t="n"/>
+      <c r="B207" s="22" t="n"/>
+      <c r="C207" s="22" t="n"/>
+      <c r="D207" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">   Завтрак-фуршет 6-8 позиций и кофе-брейк, посуда, текстиль, официанты, уборка</t>
         </is>
       </c>
-      <c r="E206" s="22" t="inlineStr">
+      <c r="E207" s="22" t="inlineStr">
         <is>
           <t>гость</t>
         </is>
       </c>
-      <c r="F206" s="23" t="n">
+      <c r="F207" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="G206" s="24">
-        <f>Прайс!E152</f>
-        <v/>
-      </c>
-      <c r="H206" s="25">
-        <f>ROUND(F206*G206,0)</f>
-        <v/>
-      </c>
-      <c r="I206" s="26" t="n">
+      <c r="G207" s="24">
+        <f>Прайс!E153</f>
+        <v/>
+      </c>
+      <c r="H207" s="25">
+        <f>ROUND(F207*G207,0)</f>
+        <v/>
+      </c>
+      <c r="I207" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J206" s="27">
-        <f>ROUND(H206*(1-I206),0)</f>
-        <v/>
-      </c>
-      <c r="K206" s="25">
-        <f>ROUND(J206*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L206" s="27">
-        <f>J206+K206</f>
-        <v/>
-      </c>
-      <c r="M206" s="8" t="n"/>
-      <c r="N206" s="8" t="n"/>
-      <c r="O206" s="22" t="n"/>
-      <c r="P206" s="8" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="19" t="n"/>
-      <c r="B207" s="19" t="n"/>
-      <c r="C207" s="19" t="n"/>
-      <c r="D207" s="20" t="inlineStr">
+      <c r="J207" s="27">
+        <f>ROUND(H207*(1-I207),0)</f>
+        <v/>
+      </c>
+      <c r="K207" s="25">
+        <f>ROUND(J207*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L207" s="27">
+        <f>J207+K207</f>
+        <v/>
+      </c>
+      <c r="M207" s="8" t="n"/>
+      <c r="N207" s="8" t="n"/>
+      <c r="O207" s="22" t="n"/>
+      <c r="P207" s="8" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="19" t="n"/>
+      <c r="B208" s="19" t="n"/>
+      <c r="C208" s="19" t="n"/>
+      <c r="D208" s="20" t="inlineStr">
         <is>
           <t>(2) Вечерний фуршет на 100 гостей, 3 ч, безалкогольный бар</t>
         </is>
       </c>
-      <c r="E207" s="9" t="inlineStr">
+      <c r="E208" s="9" t="inlineStr">
         <is>
           <t>итого</t>
         </is>
       </c>
-      <c r="F207" s="19" t="n"/>
-      <c r="G207" s="19" t="n"/>
-      <c r="H207" s="21">
-        <f>SUM(H208:H208)</f>
-        <v/>
-      </c>
-      <c r="I207" s="19" t="n"/>
-      <c r="J207" s="21">
-        <f>SUM(J208:J208)</f>
-        <v/>
-      </c>
-      <c r="K207" s="21">
-        <f>SUM(K208:K208)</f>
-        <v/>
-      </c>
-      <c r="L207" s="21">
-        <f>SUM(L208:L208)</f>
-        <v/>
-      </c>
-      <c r="M207" s="19" t="inlineStr">
+      <c r="F208" s="19" t="n"/>
+      <c r="G208" s="19" t="n"/>
+      <c r="H208" s="21">
+        <f>SUM(H209:H209)</f>
+        <v/>
+      </c>
+      <c r="I208" s="19" t="n"/>
+      <c r="J208" s="21">
+        <f>SUM(J209:J209)</f>
+        <v/>
+      </c>
+      <c r="K208" s="21">
+        <f>SUM(K209:K209)</f>
+        <v/>
+      </c>
+      <c r="L208" s="21">
+        <f>SUM(L209:L209)</f>
+        <v/>
+      </c>
+      <c r="M208" s="19" t="inlineStr">
         <is>
           <t>Заказ за 7 р.д.</t>
         </is>
       </c>
-      <c r="N207" s="19" t="n"/>
-      <c r="O207" s="19" t="n"/>
-      <c r="P207" s="19" t="n"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="22" t="n"/>
-      <c r="B208" s="22" t="n"/>
-      <c r="C208" s="22" t="n"/>
-      <c r="D208" s="8" t="inlineStr">
+      <c r="N208" s="19" t="n"/>
+      <c r="O208" s="19" t="n"/>
+      <c r="P208" s="19" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="22" t="n"/>
+      <c r="B209" s="22" t="n"/>
+      <c r="C209" s="22" t="n"/>
+      <c r="D209" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">   Вечерний фуршет 10-12 позиций и безалкогольный бар, посуда, текстиль, официанты, уборка</t>
         </is>
       </c>
-      <c r="E208" s="22" t="inlineStr">
+      <c r="E209" s="22" t="inlineStr">
         <is>
           <t>гость</t>
         </is>
       </c>
-      <c r="F208" s="23" t="n">
+      <c r="F209" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="G208" s="24">
-        <f>Прайс!E153</f>
-        <v/>
-      </c>
-      <c r="H208" s="25">
-        <f>ROUND(F208*G208,0)</f>
-        <v/>
-      </c>
-      <c r="I208" s="26" t="n">
+      <c r="G209" s="24">
+        <f>Прайс!E154</f>
+        <v/>
+      </c>
+      <c r="H209" s="25">
+        <f>ROUND(F209*G209,0)</f>
+        <v/>
+      </c>
+      <c r="I209" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J208" s="27">
-        <f>ROUND(H208*(1-I208),0)</f>
-        <v/>
-      </c>
-      <c r="K208" s="25">
-        <f>ROUND(J208*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L208" s="27">
-        <f>J208+K208</f>
-        <v/>
-      </c>
-      <c r="M208" s="8" t="n"/>
-      <c r="N208" s="8" t="n"/>
-      <c r="O208" s="22" t="n"/>
-      <c r="P208" s="8" t="n"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="19" t="n"/>
-      <c r="B209" s="19" t="n"/>
-      <c r="C209" s="19" t="n"/>
-      <c r="D209" s="20" t="inlineStr">
-        <is>
-          <t>Официант сверх нормы</t>
-        </is>
-      </c>
-      <c r="E209" s="19" t="inlineStr">
-        <is>
-          <t>час</t>
-        </is>
-      </c>
-      <c r="F209" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G209" s="32">
-        <f>Прайс!E154</f>
-        <v/>
-      </c>
-      <c r="H209" s="33">
-        <f>ROUND(F209*G209,0)</f>
-        <v/>
-      </c>
-      <c r="I209" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J209" s="35">
+      <c r="J209" s="27">
         <f>ROUND(H209*(1-I209),0)</f>
         <v/>
       </c>
-      <c r="K209" s="33">
+      <c r="K209" s="25">
         <f>ROUND(J209*Прайс!$B$5,0)</f>
         <v/>
       </c>
-      <c r="L209" s="35">
+      <c r="L209" s="27">
         <f>J209+K209</f>
         <v/>
       </c>
-      <c r="M209" s="19" t="inlineStr"/>
-      <c r="N209" s="19" t="n"/>
-      <c r="O209" s="19" t="n"/>
-      <c r="P209" s="19" t="n"/>
+      <c r="M209" s="8" t="n"/>
+      <c r="N209" s="8" t="n"/>
+      <c r="O209" s="22" t="n"/>
+      <c r="P209" s="8" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="19" t="n"/>
@@ -10815,12 +10814,12 @@
       <c r="C210" s="19" t="n"/>
       <c r="D210" s="20" t="inlineStr">
         <is>
-          <t>Дегустация</t>
+          <t>Официант сверх нормы</t>
         </is>
       </c>
       <c r="E210" s="19" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>час</t>
         </is>
       </c>
       <c r="F210" s="31" t="n">
@@ -10849,143 +10848,143 @@
         <f>J210+K210</f>
         <v/>
       </c>
-      <c r="M210" s="19" t="inlineStr">
-        <is>
-          <t>За 5 р.д. до мероприятия</t>
-        </is>
-      </c>
+      <c r="M210" s="19" t="inlineStr"/>
       <c r="N210" s="19" t="n"/>
       <c r="O210" s="19" t="n"/>
       <c r="P210" s="19" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="15" t="n">
+      <c r="A211" s="19" t="n"/>
+      <c r="B211" s="19" t="n"/>
+      <c r="C211" s="19" t="n"/>
+      <c r="D211" s="20" t="inlineStr">
+        <is>
+          <t>Дегустация</t>
+        </is>
+      </c>
+      <c r="E211" s="19" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="F211" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" s="32">
+        <f>Прайс!E156</f>
+        <v/>
+      </c>
+      <c r="H211" s="33">
+        <f>ROUND(F211*G211,0)</f>
+        <v/>
+      </c>
+      <c r="I211" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="35">
+        <f>ROUND(H211*(1-I211),0)</f>
+        <v/>
+      </c>
+      <c r="K211" s="33">
+        <f>ROUND(J211*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L211" s="35">
+        <f>J211+K211</f>
+        <v/>
+      </c>
+      <c r="M211" s="19" t="inlineStr">
+        <is>
+          <t>За 5 р.д. до мероприятия</t>
+        </is>
+      </c>
+      <c r="N211" s="19" t="n"/>
+      <c r="O211" s="19" t="n"/>
+      <c r="P211" s="19" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="B211" s="16" t="inlineStr">
+      <c r="B212" s="16" t="inlineStr">
         <is>
           <t>Звук и свет</t>
         </is>
       </c>
-      <c r="C211" s="17" t="inlineStr">
+      <c r="C212" s="17" t="inlineStr">
         <is>
           <t>Времена Года, Венеция, Центральный рынок</t>
         </is>
       </c>
-      <c r="D211" s="18" t="inlineStr">
+      <c r="D212" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E211" s="17" t="n"/>
-      <c r="F211" s="17" t="n"/>
-      <c r="G211" s="17" t="n"/>
-      <c r="H211" s="17" t="n"/>
-      <c r="I211" s="17" t="n"/>
-      <c r="J211" s="17" t="n"/>
-      <c r="K211" s="17" t="n"/>
-      <c r="L211" s="17" t="n"/>
-      <c r="M211" s="17" t="n"/>
-      <c r="N211" s="17">
+      <c r="E212" s="17" t="n"/>
+      <c r="F212" s="17" t="n"/>
+      <c r="G212" s="17" t="n"/>
+      <c r="H212" s="17" t="n"/>
+      <c r="I212" s="17" t="n"/>
+      <c r="J212" s="17" t="n"/>
+      <c r="K212" s="17" t="n"/>
+      <c r="L212" s="17" t="n"/>
+      <c r="M212" s="17" t="n"/>
+      <c r="N212" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
         <v/>
       </c>
-      <c r="O211" s="17">
+      <c r="O212" s="17">
         <f>Прайс!$B$9&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P211" s="17" t="inlineStr">
+      <c r="P212" s="17" t="inlineStr">
         <is>
           <t>Техник на площадке все время мероприятия. Резервный радиомикрофон в комплекте, резервный пульт по прайсу.</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="19" t="n"/>
-      <c r="B212" s="19" t="n"/>
-      <c r="C212" s="19" t="n"/>
-      <c r="D212" s="20" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="19" t="n"/>
+      <c r="B213" s="19" t="n"/>
+      <c r="C213" s="19" t="n"/>
+      <c r="D213" s="20" t="inlineStr">
         <is>
           <t>Мероприятие в атриуме на 100 гостей, 4 ч</t>
         </is>
       </c>
-      <c r="E212" s="9" t="inlineStr">
+      <c r="E213" s="9" t="inlineStr">
         <is>
           <t>итого</t>
         </is>
       </c>
-      <c r="F212" s="19" t="n"/>
-      <c r="G212" s="19" t="n"/>
-      <c r="H212" s="21">
-        <f>SUM(H213:H218)</f>
-        <v/>
-      </c>
-      <c r="I212" s="19" t="n"/>
-      <c r="J212" s="21">
-        <f>SUM(J213:J218)</f>
-        <v/>
-      </c>
-      <c r="K212" s="21">
-        <f>SUM(K213:K218)</f>
-        <v/>
-      </c>
-      <c r="L212" s="21">
-        <f>SUM(L213:L218)</f>
-        <v/>
-      </c>
-      <c r="M212" s="19" t="inlineStr">
+      <c r="F213" s="19" t="n"/>
+      <c r="G213" s="19" t="n"/>
+      <c r="H213" s="21">
+        <f>SUM(H214:H219)</f>
+        <v/>
+      </c>
+      <c r="I213" s="19" t="n"/>
+      <c r="J213" s="21">
+        <f>SUM(J214:J219)</f>
+        <v/>
+      </c>
+      <c r="K213" s="21">
+        <f>SUM(K214:K219)</f>
+        <v/>
+      </c>
+      <c r="L213" s="21">
+        <f>SUM(L214:L219)</f>
+        <v/>
+      </c>
+      <c r="M213" s="19" t="inlineStr">
         <is>
           <t>Монтаж 3 ч, демонтаж 1,5 ч</t>
         </is>
       </c>
-      <c r="N212" s="19" t="n"/>
-      <c r="O212" s="19" t="n"/>
-      <c r="P212" s="19" t="n"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="22" t="n"/>
-      <c r="B213" s="22" t="n"/>
-      <c r="C213" s="22" t="n"/>
-      <c r="D213" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Акустическая система на зону до 300 м²</t>
-        </is>
-      </c>
-      <c r="E213" s="22" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="F213" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G213" s="24">
-        <f>Прайс!E156</f>
-        <v/>
-      </c>
-      <c r="H213" s="25">
-        <f>ROUND(F213*G213,0)</f>
-        <v/>
-      </c>
-      <c r="I213" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J213" s="27">
-        <f>ROUND(H213*(1-I213),0)</f>
-        <v/>
-      </c>
-      <c r="K213" s="25">
-        <f>ROUND(J213*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L213" s="27">
-        <f>J213+K213</f>
-        <v/>
-      </c>
-      <c r="M213" s="8" t="n"/>
-      <c r="N213" s="8" t="n"/>
-      <c r="O213" s="22" t="n"/>
-      <c r="P213" s="8" t="n"/>
+      <c r="N213" s="19" t="n"/>
+      <c r="O213" s="19" t="n"/>
+      <c r="P213" s="19" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="22" t="n"/>
@@ -10993,16 +10992,16 @@
       <c r="C214" s="22" t="n"/>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Радиомикрофон</t>
+          <t xml:space="preserve">   Акустическая система на зону до 300 м²</t>
         </is>
       </c>
       <c r="E214" s="22" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="F214" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G214" s="24">
         <f>Прайс!E157</f>
@@ -11038,7 +11037,7 @@
       <c r="C215" s="22" t="n"/>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Микшерный пульт</t>
+          <t xml:space="preserve">   Радиомикрофон</t>
         </is>
       </c>
       <c r="E215" s="22" t="inlineStr">
@@ -11047,7 +11046,7 @@
         </is>
       </c>
       <c r="F215" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G215" s="24">
         <f>Прайс!E158</f>
@@ -11083,12 +11082,12 @@
       <c r="C216" s="22" t="n"/>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Сценический свет для подиума 4 × 3 м</t>
+          <t xml:space="preserve">   Микшерный пульт</t>
         </is>
       </c>
       <c r="E216" s="22" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="F216" s="23" t="n">
@@ -11128,12 +11127,12 @@
       <c r="C217" s="22" t="n"/>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Техник на все время мероприятия</t>
+          <t xml:space="preserve">   Сценический свет для подиума 4 × 3 м</t>
         </is>
       </c>
       <c r="E217" s="22" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="F217" s="23" t="n">
@@ -11173,12 +11172,12 @@
       <c r="C218" s="22" t="n"/>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Доставка, монтаж, демонтаж</t>
+          <t xml:space="preserve">   Техник на все время мероприятия</t>
         </is>
       </c>
       <c r="E218" s="22" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="F218" s="23" t="n">
@@ -11213,182 +11212,182 @@
       <c r="P218" s="8" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="15" t="n">
+      <c r="A219" s="22" t="n"/>
+      <c r="B219" s="22" t="n"/>
+      <c r="C219" s="22" t="n"/>
+      <c r="D219" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Доставка, монтаж, демонтаж</t>
+        </is>
+      </c>
+      <c r="E219" s="22" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="F219" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="24">
+        <f>Прайс!E162</f>
+        <v/>
+      </c>
+      <c r="H219" s="25">
+        <f>ROUND(F219*G219,0)</f>
+        <v/>
+      </c>
+      <c r="I219" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" s="27">
+        <f>ROUND(H219*(1-I219),0)</f>
+        <v/>
+      </c>
+      <c r="K219" s="25">
+        <f>ROUND(J219*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L219" s="27">
+        <f>J219+K219</f>
+        <v/>
+      </c>
+      <c r="M219" s="8" t="n"/>
+      <c r="N219" s="8" t="n"/>
+      <c r="O219" s="22" t="n"/>
+      <c r="P219" s="8" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="B219" s="16" t="inlineStr">
+      <c r="B220" s="16" t="inlineStr">
         <is>
           <t>Звукорежиссер</t>
         </is>
       </c>
-      <c r="C219" s="17" t="inlineStr">
+      <c r="C220" s="17" t="inlineStr">
         <is>
           <t>ЦДМ, Венеция, Центральный рынок</t>
         </is>
       </c>
-      <c r="D219" s="18" t="inlineStr">
+      <c r="D220" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E219" s="17" t="n"/>
-      <c r="F219" s="17" t="n"/>
-      <c r="G219" s="17" t="n"/>
-      <c r="H219" s="17" t="n"/>
-      <c r="I219" s="17" t="n"/>
-      <c r="J219" s="17" t="n"/>
-      <c r="K219" s="17" t="n"/>
-      <c r="L219" s="17" t="n"/>
-      <c r="M219" s="17" t="n"/>
-      <c r="N219" s="17">
+      <c r="E220" s="17" t="n"/>
+      <c r="F220" s="17" t="n"/>
+      <c r="G220" s="17" t="n"/>
+      <c r="H220" s="17" t="n"/>
+      <c r="I220" s="17" t="n"/>
+      <c r="J220" s="17" t="n"/>
+      <c r="K220" s="17" t="n"/>
+      <c r="L220" s="17" t="n"/>
+      <c r="M220" s="17" t="n"/>
+      <c r="N220" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
         <v/>
       </c>
-      <c r="O219" s="17">
+      <c r="O220" s="17">
         <f>Прайс!$B$9&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P219" s="17" t="inlineStr">
+      <c r="P220" s="17" t="inlineStr">
         <is>
           <t>Работа на оборудовании подрядчика по звуку или площадки.</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="19" t="n"/>
-      <c r="B220" s="19" t="n"/>
-      <c r="C220" s="19" t="n"/>
-      <c r="D220" s="20" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="19" t="n"/>
+      <c r="B221" s="19" t="n"/>
+      <c r="C221" s="19" t="n"/>
+      <c r="D221" s="20" t="inlineStr">
         <is>
           <t>Смена 6 ч: ведущий + живое выступление, вокал и гитара</t>
         </is>
       </c>
-      <c r="E220" s="19" t="inlineStr">
+      <c r="E221" s="19" t="inlineStr">
         <is>
           <t>смена</t>
         </is>
       </c>
-      <c r="F220" s="31" t="n">
+      <c r="F221" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G220" s="32">
-        <f>Прайс!E162</f>
-        <v/>
-      </c>
-      <c r="H220" s="33">
-        <f>ROUND(F220*G220,0)</f>
-        <v/>
-      </c>
-      <c r="I220" s="34" t="n">
+      <c r="G221" s="32">
+        <f>Прайс!E163</f>
+        <v/>
+      </c>
+      <c r="H221" s="33">
+        <f>ROUND(F221*G221,0)</f>
+        <v/>
+      </c>
+      <c r="I221" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J220" s="35">
-        <f>ROUND(H220*(1-I220),0)</f>
-        <v/>
-      </c>
-      <c r="K220" s="33">
-        <f>ROUND(J220*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L220" s="35">
-        <f>J220+K220</f>
-        <v/>
-      </c>
-      <c r="M220" s="19" t="inlineStr">
+      <c r="J221" s="35">
+        <f>ROUND(H221*(1-I221),0)</f>
+        <v/>
+      </c>
+      <c r="K221" s="33">
+        <f>ROUND(J221*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L221" s="35">
+        <f>J221+K221</f>
+        <v/>
+      </c>
+      <c r="M221" s="19" t="inlineStr">
         <is>
           <t>Саундчек 1 ч входит в смену</t>
         </is>
       </c>
-      <c r="N220" s="19" t="n"/>
-      <c r="O220" s="19" t="n"/>
-      <c r="P220" s="19" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="15" t="n">
+      <c r="N221" s="19" t="n"/>
+      <c r="O221" s="19" t="n"/>
+      <c r="P221" s="19" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="B221" s="16" t="inlineStr">
+      <c r="B222" s="16" t="inlineStr">
         <is>
           <t>Диджей</t>
         </is>
       </c>
-      <c r="C221" s="17" t="inlineStr">
+      <c r="C222" s="17" t="inlineStr">
         <is>
           <t>Времена Года, Венеция, Центральный рынок</t>
         </is>
       </c>
-      <c r="D221" s="18" t="inlineStr">
+      <c r="D222" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E221" s="17" t="n"/>
-      <c r="F221" s="17" t="n"/>
-      <c r="G221" s="17" t="n"/>
-      <c r="H221" s="17" t="n"/>
-      <c r="I221" s="17" t="n"/>
-      <c r="J221" s="17" t="n"/>
-      <c r="K221" s="17" t="n"/>
-      <c r="L221" s="17" t="n"/>
-      <c r="M221" s="17" t="n"/>
-      <c r="N221" s="17">
+      <c r="E222" s="17" t="n"/>
+      <c r="F222" s="17" t="n"/>
+      <c r="G222" s="17" t="n"/>
+      <c r="H222" s="17" t="n"/>
+      <c r="I222" s="17" t="n"/>
+      <c r="J222" s="17" t="n"/>
+      <c r="K222" s="17" t="n"/>
+      <c r="L222" s="17" t="n"/>
+      <c r="M222" s="17" t="n"/>
+      <c r="N222" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
         <v/>
       </c>
-      <c r="O221" s="17">
+      <c r="O222" s="17">
         <f>Прайс!$B$9&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P221" s="17" t="inlineStr">
+      <c r="P222" s="17" t="inlineStr">
         <is>
           <t>Плейлист согласуем заранее. Запись сета 20-30 мин в этом формате высылаем по запросу.</t>
         </is>
       </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="19" t="n"/>
-      <c r="B222" s="19" t="n"/>
-      <c r="C222" s="19" t="n"/>
-      <c r="D222" s="20" t="inlineStr">
-        <is>
-          <t>Сет 3 ч, lounge / deep house, с оборудованием</t>
-        </is>
-      </c>
-      <c r="E222" s="19" t="inlineStr">
-        <is>
-          <t>сет</t>
-        </is>
-      </c>
-      <c r="F222" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G222" s="32">
-        <f>Прайс!E164</f>
-        <v/>
-      </c>
-      <c r="H222" s="33">
-        <f>ROUND(F222*G222,0)</f>
-        <v/>
-      </c>
-      <c r="I222" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J222" s="35">
-        <f>ROUND(H222*(1-I222),0)</f>
-        <v/>
-      </c>
-      <c r="K222" s="33">
-        <f>ROUND(J222*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L222" s="35">
-        <f>J222+K222</f>
-        <v/>
-      </c>
-      <c r="M222" s="19" t="inlineStr"/>
-      <c r="N222" s="19" t="n"/>
-      <c r="O222" s="19" t="n"/>
-      <c r="P222" s="19" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="19" t="n"/>
@@ -11396,7 +11395,7 @@
       <c r="C223" s="19" t="n"/>
       <c r="D223" s="20" t="inlineStr">
         <is>
-          <t>Сет 3 ч, без оборудования</t>
+          <t>Сет 3 ч, lounge / deep house, с оборудованием</t>
         </is>
       </c>
       <c r="E223" s="19" t="inlineStr">
@@ -11436,133 +11435,133 @@
       <c r="P223" s="19" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="15" t="n">
+      <c r="A224" s="19" t="n"/>
+      <c r="B224" s="19" t="n"/>
+      <c r="C224" s="19" t="n"/>
+      <c r="D224" s="20" t="inlineStr">
+        <is>
+          <t>Сет 3 ч, без оборудования</t>
+        </is>
+      </c>
+      <c r="E224" s="19" t="inlineStr">
+        <is>
+          <t>сет</t>
+        </is>
+      </c>
+      <c r="F224" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="32">
+        <f>Прайс!E166</f>
+        <v/>
+      </c>
+      <c r="H224" s="33">
+        <f>ROUND(F224*G224,0)</f>
+        <v/>
+      </c>
+      <c r="I224" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" s="35">
+        <f>ROUND(H224*(1-I224),0)</f>
+        <v/>
+      </c>
+      <c r="K224" s="33">
+        <f>ROUND(J224*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L224" s="35">
+        <f>J224+K224</f>
+        <v/>
+      </c>
+      <c r="M224" s="19" t="inlineStr"/>
+      <c r="N224" s="19" t="n"/>
+      <c r="O224" s="19" t="n"/>
+      <c r="P224" s="19" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="B224" s="16" t="inlineStr">
+      <c r="B225" s="16" t="inlineStr">
         <is>
           <t>Аренда мебели</t>
         </is>
       </c>
-      <c r="C224" s="17" t="inlineStr">
+      <c r="C225" s="17" t="inlineStr">
         <is>
           <t>Времена Года, Венеция</t>
         </is>
       </c>
-      <c r="D224" s="18" t="inlineStr">
+      <c r="D225" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E224" s="17" t="n"/>
-      <c r="F224" s="17" t="n"/>
-      <c r="G224" s="17" t="n"/>
-      <c r="H224" s="17" t="n"/>
-      <c r="I224" s="17" t="n"/>
-      <c r="J224" s="17" t="n"/>
-      <c r="K224" s="17" t="n"/>
-      <c r="L224" s="17" t="n"/>
-      <c r="M224" s="17" t="n"/>
-      <c r="N224" s="17">
+      <c r="E225" s="17" t="n"/>
+      <c r="F225" s="17" t="n"/>
+      <c r="G225" s="17" t="n"/>
+      <c r="H225" s="17" t="n"/>
+      <c r="I225" s="17" t="n"/>
+      <c r="J225" s="17" t="n"/>
+      <c r="K225" s="17" t="n"/>
+      <c r="L225" s="17" t="n"/>
+      <c r="M225" s="17" t="n"/>
+      <c r="N225" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$7,"0%")&amp;", остаток "&amp;TEXT(1-Прайс!$B$7,"0%")&amp;" после акта"</f>
         <v/>
       </c>
-      <c r="O224" s="17">
+      <c r="O225" s="17">
         <f>Прайс!$B$10&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P224" s="17" t="inlineStr">
+      <c r="P225" s="17" t="inlineStr">
         <is>
           <t>Залог не берем, работаем по договору. Повреждения фиксируем актом и возмещаем по прайсу прокатчика. Минимальный заказ 30 000 ₽ без НДС.</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="19" t="n"/>
-      <c r="B225" s="19" t="n"/>
-      <c r="C225" s="19" t="n"/>
-      <c r="D225" s="20" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="19" t="n"/>
+      <c r="B226" s="19" t="n"/>
+      <c r="C226" s="19" t="n"/>
+      <c r="D226" s="20" t="inlineStr">
         <is>
           <t>Мероприятие на 100 гостей, 1 день: 3 лаунж-зоны, 10 коктейльных столов, барная стойка</t>
         </is>
       </c>
-      <c r="E225" s="9" t="inlineStr">
+      <c r="E226" s="9" t="inlineStr">
         <is>
           <t>итого</t>
         </is>
       </c>
-      <c r="F225" s="19" t="n"/>
-      <c r="G225" s="19" t="n"/>
-      <c r="H225" s="21">
-        <f>SUM(H226:H229)</f>
-        <v/>
-      </c>
-      <c r="I225" s="19" t="n"/>
-      <c r="J225" s="21">
-        <f>SUM(J226:J229)</f>
-        <v/>
-      </c>
-      <c r="K225" s="21">
-        <f>SUM(K226:K229)</f>
-        <v/>
-      </c>
-      <c r="L225" s="21">
-        <f>SUM(L226:L229)</f>
-        <v/>
-      </c>
-      <c r="M225" s="19" t="inlineStr">
+      <c r="F226" s="19" t="n"/>
+      <c r="G226" s="19" t="n"/>
+      <c r="H226" s="21">
+        <f>SUM(H227:H230)</f>
+        <v/>
+      </c>
+      <c r="I226" s="19" t="n"/>
+      <c r="J226" s="21">
+        <f>SUM(J227:J230)</f>
+        <v/>
+      </c>
+      <c r="K226" s="21">
+        <f>SUM(K227:K230)</f>
+        <v/>
+      </c>
+      <c r="L226" s="21">
+        <f>SUM(L227:L230)</f>
+        <v/>
+      </c>
+      <c r="M226" s="19" t="inlineStr">
         <is>
           <t>Бронь за 5 р.д.</t>
         </is>
       </c>
-      <c r="N225" s="19" t="n"/>
-      <c r="O225" s="19" t="n"/>
-      <c r="P225" s="19" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="22" t="n"/>
-      <c r="B226" s="22" t="n"/>
-      <c r="C226" s="22" t="n"/>
-      <c r="D226" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Лаунж-зона: диван, 2 кресла, журнальный стол</t>
-        </is>
-      </c>
-      <c r="E226" s="22" t="inlineStr">
-        <is>
-          <t>компл./сут.</t>
-        </is>
-      </c>
-      <c r="F226" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G226" s="24">
-        <f>Прайс!E167</f>
-        <v/>
-      </c>
-      <c r="H226" s="25">
-        <f>ROUND(F226*G226,0)</f>
-        <v/>
-      </c>
-      <c r="I226" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J226" s="27">
-        <f>ROUND(H226*(1-I226),0)</f>
-        <v/>
-      </c>
-      <c r="K226" s="25">
-        <f>ROUND(J226*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L226" s="27">
-        <f>J226+K226</f>
-        <v/>
-      </c>
-      <c r="M226" s="8" t="n"/>
-      <c r="N226" s="8" t="n"/>
-      <c r="O226" s="22" t="n"/>
-      <c r="P226" s="8" t="n"/>
+      <c r="N226" s="19" t="n"/>
+      <c r="O226" s="19" t="n"/>
+      <c r="P226" s="19" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="22" t="n"/>
@@ -11570,16 +11569,16 @@
       <c r="C227" s="22" t="n"/>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Коктейльный стол с чехлом</t>
+          <t xml:space="preserve">   Лаунж-зона: диван, 2 кресла, журнальный стол</t>
         </is>
       </c>
       <c r="E227" s="22" t="inlineStr">
         <is>
-          <t>шт./сут.</t>
+          <t>компл./сут.</t>
         </is>
       </c>
       <c r="F227" s="23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G227" s="24">
         <f>Прайс!E168</f>
@@ -11615,7 +11614,7 @@
       <c r="C228" s="22" t="n"/>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Барная стойка</t>
+          <t xml:space="preserve">   Коктейльный стол с чехлом</t>
         </is>
       </c>
       <c r="E228" s="22" t="inlineStr">
@@ -11624,7 +11623,7 @@
         </is>
       </c>
       <c r="F228" s="23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G228" s="24">
         <f>Прайс!E169</f>
@@ -11660,12 +11659,12 @@
       <c r="C229" s="22" t="n"/>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Доставка, сборка и вывоз в ночное время</t>
+          <t xml:space="preserve">   Барная стойка</t>
         </is>
       </c>
       <c r="E229" s="22" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт./сут.</t>
         </is>
       </c>
       <c r="F229" s="23" t="n">
@@ -11697,119 +11696,124 @@
       <c r="M229" s="8" t="n"/>
       <c r="N229" s="8" t="n"/>
       <c r="O229" s="22" t="n"/>
-      <c r="P229" s="8" t="inlineStr">
+      <c r="P229" s="8" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="22" t="n"/>
+      <c r="B230" s="22" t="n"/>
+      <c r="C230" s="22" t="n"/>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Доставка, сборка и вывоз в ночное время</t>
+        </is>
+      </c>
+      <c r="E230" s="22" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="F230" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" s="24">
+        <f>Прайс!E171</f>
+        <v/>
+      </c>
+      <c r="H230" s="25">
+        <f>ROUND(F230*G230,0)</f>
+        <v/>
+      </c>
+      <c r="I230" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="27">
+        <f>ROUND(H230*(1-I230),0)</f>
+        <v/>
+      </c>
+      <c r="K230" s="25">
+        <f>ROUND(J230*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L230" s="27">
+        <f>J230+K230</f>
+        <v/>
+      </c>
+      <c r="M230" s="8" t="n"/>
+      <c r="N230" s="8" t="n"/>
+      <c r="O230" s="22" t="n"/>
+      <c r="P230" s="8" t="inlineStr">
         <is>
           <t>ночью</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="15" t="n">
+    <row r="231">
+      <c r="A231" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="B230" s="16" t="inlineStr">
+      <c r="B231" s="16" t="inlineStr">
         <is>
           <t>Закупка мебели</t>
         </is>
       </c>
-      <c r="C230" s="17" t="inlineStr">
+      <c r="C231" s="17" t="inlineStr">
         <is>
           <t>Времена Года, Венеция</t>
         </is>
       </c>
-      <c r="D230" s="18" t="inlineStr">
+      <c r="D231" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E230" s="17" t="n"/>
-      <c r="F230" s="17" t="n"/>
-      <c r="G230" s="17" t="n"/>
-      <c r="H230" s="17" t="n"/>
-      <c r="I230" s="17" t="n"/>
-      <c r="J230" s="17" t="n"/>
-      <c r="K230" s="17" t="n"/>
-      <c r="L230" s="17" t="n"/>
-      <c r="M230" s="17" t="n"/>
-      <c r="N230" s="17">
+      <c r="E231" s="17" t="n"/>
+      <c r="F231" s="17" t="n"/>
+      <c r="G231" s="17" t="n"/>
+      <c r="H231" s="17" t="n"/>
+      <c r="I231" s="17" t="n"/>
+      <c r="J231" s="17" t="n"/>
+      <c r="K231" s="17" t="n"/>
+      <c r="L231" s="17" t="n"/>
+      <c r="M231" s="17" t="n"/>
+      <c r="N231" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$7,"0%")&amp;", остаток "&amp;TEXT(1-Прайс!$B$7,"0%")&amp;" после акта"</f>
         <v/>
       </c>
-      <c r="O230" s="17">
+      <c r="O231" s="17">
         <f>Прайс!$B$10&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P230" s="17" t="inlineStr">
+      <c r="P231" s="17" t="inlineStr">
         <is>
           <t>Подбираем модели российских фабрик контрактной мебели с сертификатами соответствия и пожарной безопасности на мебель и ткани. Гарантия 12 месяцев. Изготовление под размер возможно, срок дольше на 10-15 р.д.</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="19" t="n"/>
-      <c r="B231" s="19" t="n"/>
-      <c r="C231" s="19" t="n"/>
-      <c r="D231" s="20" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="19" t="n"/>
+      <c r="B232" s="19" t="n"/>
+      <c r="C232" s="19" t="n"/>
+      <c r="D232" s="20" t="inlineStr">
         <is>
           <t>Зона отдыха: 6 диванов, 12 кресел, 6 столиков, ткань от 50 000 циклов по Мартиндейлу</t>
         </is>
       </c>
-      <c r="E231" s="19" t="n"/>
-      <c r="F231" s="19" t="n"/>
-      <c r="G231" s="19" t="n"/>
-      <c r="H231" s="19" t="n"/>
-      <c r="I231" s="19" t="n"/>
-      <c r="J231" s="19" t="n"/>
-      <c r="K231" s="19" t="n"/>
-      <c r="L231" s="19" t="n"/>
-      <c r="M231" s="19" t="inlineStr">
+      <c r="E232" s="19" t="n"/>
+      <c r="F232" s="19" t="n"/>
+      <c r="G232" s="19" t="n"/>
+      <c r="H232" s="19" t="n"/>
+      <c r="I232" s="19" t="n"/>
+      <c r="J232" s="19" t="n"/>
+      <c r="K232" s="19" t="n"/>
+      <c r="L232" s="19" t="n"/>
+      <c r="M232" s="19" t="inlineStr">
         <is>
           <t>Подборка 2-3 моделей с ценами за 3 р.д., поставка 30-45 р.д.</t>
         </is>
       </c>
-      <c r="N231" s="19" t="n"/>
-      <c r="O231" s="19" t="n"/>
-      <c r="P231" s="19" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="22" t="n"/>
-      <c r="B232" s="22" t="n"/>
-      <c r="C232" s="22" t="n"/>
-      <c r="D232" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Диван для общественной зоны, ткань от 50 000 циклов по Мартиндейлу</t>
-        </is>
-      </c>
-      <c r="E232" s="22" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F232" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="G232" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="H232" s="22" t="n"/>
-      <c r="I232" s="29" t="n"/>
-      <c r="J232" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="K232" s="22" t="n"/>
-      <c r="L232" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="M232" s="8" t="n"/>
-      <c r="N232" s="8" t="n"/>
-      <c r="O232" s="22" t="n"/>
-      <c r="P232" s="8" t="n"/>
+      <c r="N232" s="19" t="n"/>
+      <c r="O232" s="19" t="n"/>
+      <c r="P232" s="19" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="22" t="n"/>
@@ -11817,7 +11821,7 @@
       <c r="C233" s="22" t="n"/>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Кресло для общественной зоны, та же ткань</t>
+          <t xml:space="preserve">   Диван для общественной зоны, ткань от 50 000 циклов по Мартиндейлу</t>
         </is>
       </c>
       <c r="E233" s="22" t="inlineStr">
@@ -11826,7 +11830,7 @@
         </is>
       </c>
       <c r="F233" s="23" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G233" s="28" t="inlineStr">
         <is>
@@ -11857,7 +11861,7 @@
       <c r="C234" s="22" t="n"/>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Столик для зоны отдыха</t>
+          <t xml:space="preserve">   Кресло для общественной зоны, та же ткань</t>
         </is>
       </c>
       <c r="E234" s="22" t="inlineStr">
@@ -11866,7 +11870,7 @@
         </is>
       </c>
       <c r="F234" s="23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G234" s="28" t="inlineStr">
         <is>
@@ -11897,16 +11901,16 @@
       <c r="C235" s="22" t="n"/>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Доставка, сборка, вывоз упаковки</t>
+          <t xml:space="preserve">   Столик для зоны отдыха</t>
         </is>
       </c>
       <c r="E235" s="22" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="F235" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G235" s="28" t="inlineStr">
         <is>
@@ -11932,137 +11936,128 @@
       <c r="P235" s="8" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="15" t="n">
+      <c r="A236" s="22" t="n"/>
+      <c r="B236" s="22" t="n"/>
+      <c r="C236" s="22" t="n"/>
+      <c r="D236" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Доставка, сборка, вывоз упаковки</t>
+        </is>
+      </c>
+      <c r="E236" s="22" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="F236" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G236" s="28" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="H236" s="22" t="n"/>
+      <c r="I236" s="29" t="n"/>
+      <c r="J236" s="28" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="K236" s="22" t="n"/>
+      <c r="L236" s="28" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="M236" s="8" t="n"/>
+      <c r="N236" s="8" t="n"/>
+      <c r="O236" s="22" t="n"/>
+      <c r="P236" s="8" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="B236" s="16" t="inlineStr">
+      <c r="B237" s="16" t="inlineStr">
         <is>
           <t>Стажеры, персонал</t>
         </is>
       </c>
-      <c r="C236" s="17" t="inlineStr">
+      <c r="C237" s="17" t="inlineStr">
         <is>
           <t>Времена Года, Венеция, ЦДМ</t>
         </is>
       </c>
-      <c r="D236" s="18" t="inlineStr">
+      <c r="D237" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E236" s="17" t="n"/>
-      <c r="F236" s="17" t="n"/>
-      <c r="G236" s="17" t="n"/>
-      <c r="H236" s="17" t="n"/>
-      <c r="I236" s="17" t="n"/>
-      <c r="J236" s="17" t="n"/>
-      <c r="K236" s="17" t="n"/>
-      <c r="L236" s="17" t="n"/>
-      <c r="M236" s="17" t="n"/>
-      <c r="N236" s="17">
+      <c r="E237" s="17" t="n"/>
+      <c r="F237" s="17" t="n"/>
+      <c r="G237" s="17" t="n"/>
+      <c r="H237" s="17" t="n"/>
+      <c r="I237" s="17" t="n"/>
+      <c r="J237" s="17" t="n"/>
+      <c r="K237" s="17" t="n"/>
+      <c r="L237" s="17" t="n"/>
+      <c r="M237" s="17" t="n"/>
+      <c r="N237" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
         <v/>
       </c>
-      <c r="O236" s="17">
+      <c r="O237" s="17">
         <f>Прайс!$B$9&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P236" s="17" t="inlineStr">
+      <c r="P237" s="17" t="inlineStr">
         <is>
           <t>Оформление по ГПХ и через самозанятых. При неявке выводим замену в течение 3 ч, часы неявки к оплате не выставляем. Инструктаж перед выходом. Медкнижки при работе с едой.</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="19" t="n"/>
-      <c r="B237" s="19" t="n"/>
-      <c r="C237" s="19" t="n"/>
-      <c r="D237" s="20" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="19" t="n"/>
+      <c r="B238" s="19" t="n"/>
+      <c r="C238" s="19" t="n"/>
+      <c r="D238" s="20" t="inlineStr">
         <is>
           <t>Выходные сб-вс, по 1 смене 8 ч в день: 4 промоутера + 2 хостес с английским</t>
         </is>
       </c>
-      <c r="E237" s="9" t="inlineStr">
+      <c r="E238" s="9" t="inlineStr">
         <is>
           <t>итого</t>
         </is>
       </c>
-      <c r="F237" s="19" t="n"/>
-      <c r="G237" s="19" t="n"/>
-      <c r="H237" s="21">
-        <f>SUM(H238:H239)</f>
-        <v/>
-      </c>
-      <c r="I237" s="19" t="n"/>
-      <c r="J237" s="21">
-        <f>SUM(J238:J239)</f>
-        <v/>
-      </c>
-      <c r="K237" s="21">
-        <f>SUM(K238:K239)</f>
-        <v/>
-      </c>
-      <c r="L237" s="21">
-        <f>SUM(L238:L239)</f>
-        <v/>
-      </c>
-      <c r="M237" s="19" t="inlineStr">
+      <c r="F238" s="19" t="n"/>
+      <c r="G238" s="19" t="n"/>
+      <c r="H238" s="21">
+        <f>SUM(H239:H240)</f>
+        <v/>
+      </c>
+      <c r="I238" s="19" t="n"/>
+      <c r="J238" s="21">
+        <f>SUM(J239:J240)</f>
+        <v/>
+      </c>
+      <c r="K238" s="21">
+        <f>SUM(K239:K240)</f>
+        <v/>
+      </c>
+      <c r="L238" s="21">
+        <f>SUM(L239:L240)</f>
+        <v/>
+      </c>
+      <c r="M238" s="19" t="inlineStr">
         <is>
           <t>Выход через 3 р.д. после заявки</t>
         </is>
       </c>
-      <c r="N237" s="19" t="n"/>
-      <c r="O237" s="19" t="n"/>
-      <c r="P237" s="19" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="22" t="n"/>
-      <c r="B238" s="22" t="n"/>
-      <c r="C238" s="22" t="n"/>
-      <c r="D238" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Промоутер</t>
-        </is>
-      </c>
-      <c r="E238" s="22" t="inlineStr">
-        <is>
-          <t>час</t>
-        </is>
-      </c>
-      <c r="F238" s="23" t="n">
-        <v>64</v>
-      </c>
-      <c r="G238" s="24">
-        <f>Прайс!E175</f>
-        <v/>
-      </c>
-      <c r="H238" s="25">
-        <f>ROUND(F238*G238,0)</f>
-        <v/>
-      </c>
-      <c r="I238" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J238" s="27">
-        <f>ROUND(H238*(1-I238),0)</f>
-        <v/>
-      </c>
-      <c r="K238" s="25">
-        <f>ROUND(J238*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L238" s="27">
-        <f>J238+K238</f>
-        <v/>
-      </c>
-      <c r="M238" s="8" t="n"/>
-      <c r="N238" s="8" t="n"/>
-      <c r="O238" s="22" t="n"/>
-      <c r="P238" s="8" t="inlineStr">
-        <is>
-          <t>4 чел. × 2 смены × 8 ч</t>
-        </is>
-      </c>
+      <c r="N238" s="19" t="n"/>
+      <c r="O238" s="19" t="n"/>
+      <c r="P238" s="19" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="22" t="n"/>
@@ -12070,7 +12065,7 @@
       <c r="C239" s="22" t="n"/>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Хостес со знанием английского</t>
+          <t xml:space="preserve">   Промоутер</t>
         </is>
       </c>
       <c r="E239" s="22" t="inlineStr">
@@ -12079,7 +12074,7 @@
         </is>
       </c>
       <c r="F239" s="23" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="G239" s="24">
         <f>Прайс!E176</f>
@@ -12109,170 +12104,175 @@
       <c r="O239" s="22" t="n"/>
       <c r="P239" s="8" t="inlineStr">
         <is>
+          <t>4 чел. × 2 смены × 8 ч</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="22" t="n"/>
+      <c r="B240" s="22" t="n"/>
+      <c r="C240" s="22" t="n"/>
+      <c r="D240" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Хостес со знанием английского</t>
+        </is>
+      </c>
+      <c r="E240" s="22" t="inlineStr">
+        <is>
+          <t>час</t>
+        </is>
+      </c>
+      <c r="F240" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="G240" s="24">
+        <f>Прайс!E177</f>
+        <v/>
+      </c>
+      <c r="H240" s="25">
+        <f>ROUND(F240*G240,0)</f>
+        <v/>
+      </c>
+      <c r="I240" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" s="27">
+        <f>ROUND(H240*(1-I240),0)</f>
+        <v/>
+      </c>
+      <c r="K240" s="25">
+        <f>ROUND(J240*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L240" s="27">
+        <f>J240+K240</f>
+        <v/>
+      </c>
+      <c r="M240" s="8" t="n"/>
+      <c r="N240" s="8" t="n"/>
+      <c r="O240" s="22" t="n"/>
+      <c r="P240" s="8" t="inlineStr">
+        <is>
           <t>2 чел. × 2 смены × 8 ч</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="19" t="n"/>
-      <c r="B240" s="19" t="n"/>
-      <c r="C240" s="19" t="n"/>
-      <c r="D240" s="20" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="19" t="n"/>
+      <c r="B241" s="19" t="n"/>
+      <c r="C241" s="19" t="n"/>
+      <c r="D241" s="20" t="inlineStr">
         <is>
           <t>Брендированная форма, опция</t>
         </is>
       </c>
-      <c r="E240" s="19" t="inlineStr">
+      <c r="E241" s="19" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="F240" s="31" t="n">
+      <c r="F241" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="G240" s="32">
-        <f>Прайс!E179</f>
-        <v/>
-      </c>
-      <c r="H240" s="33">
-        <f>ROUND(F240*G240,0)</f>
-        <v/>
-      </c>
-      <c r="I240" s="34" t="n">
+      <c r="G241" s="32">
+        <f>Прайс!E180</f>
+        <v/>
+      </c>
+      <c r="H241" s="33">
+        <f>ROUND(F241*G241,0)</f>
+        <v/>
+      </c>
+      <c r="I241" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="J240" s="35">
-        <f>ROUND(H240*(1-I240),0)</f>
-        <v/>
-      </c>
-      <c r="K240" s="33">
-        <f>ROUND(J240*Прайс!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="L240" s="35">
-        <f>J240+K240</f>
-        <v/>
-      </c>
-      <c r="M240" s="19" t="inlineStr">
+      <c r="J241" s="35">
+        <f>ROUND(H241*(1-I241),0)</f>
+        <v/>
+      </c>
+      <c r="K241" s="33">
+        <f>ROUND(J241*Прайс!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="L241" s="35">
+        <f>J241+K241</f>
+        <v/>
+      </c>
+      <c r="M241" s="19" t="inlineStr">
         <is>
           <t>5 р.д.</t>
         </is>
       </c>
-      <c r="N240" s="19" t="n"/>
-      <c r="O240" s="19" t="n"/>
-      <c r="P240" s="19" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="15" t="n">
+      <c r="N241" s="19" t="n"/>
+      <c r="O241" s="19" t="n"/>
+      <c r="P241" s="19" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="B241" s="16" t="inlineStr">
+      <c r="B242" s="16" t="inlineStr">
         <is>
           <t>Фотозона</t>
         </is>
       </c>
-      <c r="C241" s="17" t="inlineStr">
+      <c r="C242" s="17" t="inlineStr">
         <is>
           <t>Венеция</t>
         </is>
       </c>
-      <c r="D241" s="18" t="inlineStr">
+      <c r="D242" s="18" t="inlineStr">
         <is>
           <t>Позиция ТЗ</t>
         </is>
       </c>
-      <c r="E241" s="17" t="n"/>
-      <c r="F241" s="17" t="n"/>
-      <c r="G241" s="17" t="n"/>
-      <c r="H241" s="17" t="n"/>
-      <c r="I241" s="17" t="n"/>
-      <c r="J241" s="17" t="n"/>
-      <c r="K241" s="17" t="n"/>
-      <c r="L241" s="17" t="n"/>
-      <c r="M241" s="17" t="n"/>
-      <c r="N241" s="17">
+      <c r="E242" s="17" t="n"/>
+      <c r="F242" s="17" t="n"/>
+      <c r="G242" s="17" t="n"/>
+      <c r="H242" s="17" t="n"/>
+      <c r="I242" s="17" t="n"/>
+      <c r="J242" s="17" t="n"/>
+      <c r="K242" s="17" t="n"/>
+      <c r="L242" s="17" t="n"/>
+      <c r="M242" s="17" t="n"/>
+      <c r="N242" s="17">
         <f>"Аванс "&amp;TEXT(Прайс!$B$7,"0%")&amp;", остаток "&amp;TEXT(1-Прайс!$B$7,"0%")&amp;" после акта"</f>
         <v/>
       </c>
-      <c r="O241" s="17">
+      <c r="O242" s="17">
         <f>Прайс!$B$10&amp;" мес."</f>
         <v/>
       </c>
-      <c r="P241" s="17" t="inlineStr">
+      <c r="P242" s="17" t="inlineStr">
         <is>
           <t>Считаем после чертежей и осмотра стены: панели «водная рябь» и пол с фигурным краем делаются под проект, каркас зависит от основания. Зеркальный пол заклеиваем антискользящей защитной пленкой: гости ходят по нему каждый день.</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="19" t="n"/>
-      <c r="B242" s="19" t="n"/>
-      <c r="C242" s="19" t="n"/>
-      <c r="D242" s="20" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="19" t="n"/>
+      <c r="B243" s="19" t="n"/>
+      <c r="C243" s="19" t="n"/>
+      <c r="D243" s="20" t="inlineStr">
         <is>
           <t>Зеркальная стена 12106 × 3600 мм, пол 12106 × 2000 мм, лайтбокс-логотип 2200 × 1500 мм</t>
         </is>
       </c>
-      <c r="E242" s="19" t="n"/>
-      <c r="F242" s="19" t="n"/>
-      <c r="G242" s="19" t="n"/>
-      <c r="H242" s="19" t="n"/>
-      <c r="I242" s="19" t="n"/>
-      <c r="J242" s="19" t="n"/>
-      <c r="K242" s="19" t="n"/>
-      <c r="L242" s="19" t="n"/>
-      <c r="M242" s="19" t="inlineStr">
+      <c r="E243" s="19" t="n"/>
+      <c r="F243" s="19" t="n"/>
+      <c r="G243" s="19" t="n"/>
+      <c r="H243" s="19" t="n"/>
+      <c r="I243" s="19" t="n"/>
+      <c r="J243" s="19" t="n"/>
+      <c r="K243" s="19" t="n"/>
+      <c r="L243" s="19" t="n"/>
+      <c r="M243" s="19" t="inlineStr">
         <is>
           <t>Расчет за 3 р.д. после чертежей и выезда на объект</t>
         </is>
       </c>
-      <c r="N242" s="19" t="n"/>
-      <c r="O242" s="19" t="n"/>
-      <c r="P242" s="19" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="22" t="n"/>
-      <c r="B243" s="22" t="n"/>
-      <c r="C243" s="22" t="n"/>
-      <c r="D243" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Зеркальные панели «водная рябь» на каркасе, стена</t>
-        </is>
-      </c>
-      <c r="E243" s="22" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="F243" s="23" t="n">
-        <v>43.58</v>
-      </c>
-      <c r="G243" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="H243" s="22" t="n"/>
-      <c r="I243" s="29" t="n"/>
-      <c r="J243" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="K243" s="22" t="n"/>
-      <c r="L243" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="M243" s="8" t="n"/>
-      <c r="N243" s="8" t="n"/>
-      <c r="O243" s="22" t="n"/>
-      <c r="P243" s="8" t="inlineStr">
-        <is>
-          <t>12,106 × 3,6 м</t>
-        </is>
-      </c>
+      <c r="N243" s="19" t="n"/>
+      <c r="O243" s="19" t="n"/>
+      <c r="P243" s="19" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="22" t="n"/>
@@ -12280,7 +12280,7 @@
       <c r="C244" s="22" t="n"/>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Напольное покрытие, зеркальный пластик, край волной</t>
+          <t xml:space="preserve">   Зеркальные панели «водная рябь» на каркасе, стена</t>
         </is>
       </c>
       <c r="E244" s="22" t="inlineStr">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="F244" s="23" t="n">
-        <v>24.21</v>
+        <v>43.58</v>
       </c>
       <c r="G244" s="28" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
       <c r="O244" s="22" t="n"/>
       <c r="P244" s="8" t="inlineStr">
         <is>
-          <t>12,106 × 2,0 м</t>
+          <t>12,106 × 3,6 м</t>
         </is>
       </c>
     </row>
@@ -12324,16 +12324,16 @@
       <c r="C245" s="22" t="n"/>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Световой лайтбокс в форме логотипа 2200 × 1500 мм</t>
+          <t xml:space="preserve">   Напольное покрытие, зеркальный пластик, край волной</t>
         </is>
       </c>
       <c r="E245" s="22" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="F245" s="23" t="n">
-        <v>1</v>
+        <v>24.21</v>
       </c>
       <c r="G245" s="28" t="inlineStr">
         <is>
@@ -12356,73 +12356,77 @@
       <c r="M245" s="8" t="n"/>
       <c r="N245" s="8" t="n"/>
       <c r="O245" s="22" t="n"/>
-      <c r="P245" s="8" t="n"/>
+      <c r="P245" s="8" t="inlineStr">
+        <is>
+          <t>12,106 × 2,0 м</t>
+        </is>
+      </c>
     </row>
     <row r="246">
-      <c r="A246" s="19" t="n"/>
-      <c r="B246" s="19" t="n"/>
-      <c r="C246" s="19" t="n"/>
-      <c r="D246" s="20" t="inlineStr">
+      <c r="A246" s="22" t="n"/>
+      <c r="B246" s="22" t="n"/>
+      <c r="C246" s="22" t="n"/>
+      <c r="D246" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Световой лайтбокс в форме логотипа 2200 × 1500 мм</t>
+        </is>
+      </c>
+      <c r="E246" s="22" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F246" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G246" s="28" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="H246" s="22" t="n"/>
+      <c r="I246" s="29" t="n"/>
+      <c r="J246" s="28" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="K246" s="22" t="n"/>
+      <c r="L246" s="28" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="M246" s="8" t="n"/>
+      <c r="N246" s="8" t="n"/>
+      <c r="O246" s="22" t="n"/>
+      <c r="P246" s="8" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="19" t="n"/>
+      <c r="B247" s="19" t="n"/>
+      <c r="C247" s="19" t="n"/>
+      <c r="D247" s="20" t="inlineStr">
         <is>
           <t>Монтаж и демонтаж</t>
         </is>
       </c>
-      <c r="E246" s="19" t="n"/>
-      <c r="F246" s="19" t="n"/>
-      <c r="G246" s="19" t="n"/>
-      <c r="H246" s="19" t="n"/>
-      <c r="I246" s="19" t="n"/>
-      <c r="J246" s="19" t="n"/>
-      <c r="K246" s="19" t="n"/>
-      <c r="L246" s="19" t="n"/>
-      <c r="M246" s="19" t="inlineStr">
+      <c r="E247" s="19" t="n"/>
+      <c r="F247" s="19" t="n"/>
+      <c r="G247" s="19" t="n"/>
+      <c r="H247" s="19" t="n"/>
+      <c r="I247" s="19" t="n"/>
+      <c r="J247" s="19" t="n"/>
+      <c r="K247" s="19" t="n"/>
+      <c r="L247" s="19" t="n"/>
+      <c r="M247" s="19" t="inlineStr">
         <is>
           <t>Монтаж 1 ночь, демонтаж 1 ночь</t>
         </is>
       </c>
-      <c r="N246" s="19" t="n"/>
-      <c r="O246" s="19" t="n"/>
-      <c r="P246" s="19" t="n"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="22" t="n"/>
-      <c r="B247" s="22" t="n"/>
-      <c r="C247" s="22" t="n"/>
-      <c r="D247" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Монтаж фотозоны</t>
-        </is>
-      </c>
-      <c r="E247" s="22" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="F247" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G247" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="H247" s="22" t="n"/>
-      <c r="I247" s="29" t="n"/>
-      <c r="J247" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="K247" s="22" t="n"/>
-      <c r="L247" s="28" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="M247" s="8" t="n"/>
-      <c r="N247" s="8" t="n"/>
-      <c r="O247" s="22" t="n"/>
-      <c r="P247" s="8" t="n"/>
+      <c r="N247" s="19" t="n"/>
+      <c r="O247" s="19" t="n"/>
+      <c r="P247" s="19" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="22" t="n"/>
@@ -12430,7 +12434,7 @@
       <c r="C248" s="22" t="n"/>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Демонтаж фотозоны</t>
+          <t xml:space="preserve">   Монтаж фотозоны</t>
         </is>
       </c>
       <c r="E248" s="22" t="inlineStr">
@@ -12464,8 +12468,48 @@
       <c r="O248" s="22" t="n"/>
       <c r="P248" s="8" t="n"/>
     </row>
+    <row r="249">
+      <c r="A249" s="22" t="n"/>
+      <c r="B249" s="22" t="n"/>
+      <c r="C249" s="22" t="n"/>
+      <c r="D249" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Демонтаж фотозоны</t>
+        </is>
+      </c>
+      <c r="E249" s="22" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="F249" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G249" s="28" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="H249" s="22" t="n"/>
+      <c r="I249" s="29" t="n"/>
+      <c r="J249" s="28" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="K249" s="22" t="n"/>
+      <c r="L249" s="28" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="M249" s="8" t="n"/>
+      <c r="N249" s="8" t="n"/>
+      <c r="O249" s="22" t="n"/>
+      <c r="P249" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P248"/>
+  <autoFilter ref="A4:P249"/>
   <mergeCells count="1">
     <mergeCell ref="A2:P2"/>
   </mergeCells>
@@ -12480,7 +12524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G184"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13042,7 +13086,7 @@
         </is>
       </c>
       <c r="E27" s="44" t="n">
-        <v>6000</v>
+        <v>6800</v>
       </c>
       <c r="F27" s="45">
         <f>E27</f>
@@ -13070,7 +13114,7 @@
         </is>
       </c>
       <c r="E28" s="44" t="n">
-        <v>8000</v>
+        <v>8800</v>
       </c>
       <c r="F28" s="45">
         <f>E28</f>
@@ -13154,7 +13198,7 @@
         </is>
       </c>
       <c r="E31" s="44" t="n">
-        <v>4500</v>
+        <v>4800</v>
       </c>
       <c r="F31" s="45">
         <f>E31</f>
@@ -13370,7 +13414,7 @@
         </is>
       </c>
       <c r="E38" s="44" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="F38" s="45">
         <f>E38</f>
@@ -13458,7 +13502,7 @@
         </is>
       </c>
       <c r="E41" s="44" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F41" s="45">
         <f>E41</f>
@@ -13486,7 +13530,7 @@
         </is>
       </c>
       <c r="E42" s="44" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F42" s="45">
         <f>E42</f>
@@ -14566,7 +14610,7 @@
         </is>
       </c>
       <c r="E78" s="44" t="n">
-        <v>45000</v>
+        <v>48000</v>
       </c>
       <c r="F78" s="45">
         <f>E78</f>
@@ -15101,7 +15145,7 @@
         <v>30000</v>
       </c>
       <c r="F96" s="45">
-        <f>ROUND(E96*(1-Прайс!$B$6),0)</f>
+        <f>E96</f>
         <v/>
       </c>
       <c r="G96" s="8" t="inlineStr">
@@ -15511,7 +15555,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Наполнение по согласованному списку</t>
+          <t>Наполнение по согласованному списку, бюджет до 5 000 ₽</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -15528,7 +15572,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>По бюджету заказчика, без наценки</t>
+          <t>По чекам</t>
         </is>
       </c>
     </row>
@@ -15543,7 +15587,7 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Сборка и упаковка</t>
+          <t>Закупка, проверка и логистика наполнения, 25% от бюджета</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -15552,7 +15596,7 @@
         </is>
       </c>
       <c r="E111" s="44" t="n">
-        <v>350</v>
+        <v>1250</v>
       </c>
       <c r="F111" s="45">
         <f>E111</f>
@@ -15571,16 +15615,16 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Курьерская доставка по Москве, фото вручения</t>
+          <t>Сборка и упаковка</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>адрес</t>
+          <t>бокс</t>
         </is>
       </c>
       <c r="E112" s="44" t="n">
-        <v>950</v>
+        <v>350</v>
       </c>
       <c r="F112" s="45">
         <f>E112</f>
@@ -15590,25 +15634,25 @@
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>Брендированная вода</t>
+          <t>Сувенирная продукция, PR-боксы</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Вода негазированная 0,33 л ПЭТ, полноцветная этикетка, партия 1 000</t>
+          <t>Курьерская доставка по Москве, фото вручения</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>адрес</t>
         </is>
       </c>
       <c r="E113" s="44" t="n">
-        <v>58</v>
+        <v>950</v>
       </c>
       <c r="F113" s="45">
         <f>E113</f>
@@ -15627,7 +15671,7 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Вода негазированная 0,33 л ПЭТ, полноцветная этикетка, партия 5 000</t>
+          <t>Вода негазированная 0,33 л ПЭТ, полноцветная этикетка, партия 1 000</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -15636,7 +15680,7 @@
         </is>
       </c>
       <c r="E114" s="44" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F114" s="45">
         <f>E114</f>
@@ -15655,7 +15699,7 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Вода 0,33 л в стекле, полноцветная этикетка, партия 1 000</t>
+          <t>Вода негазированная 0,33 л ПЭТ, полноцветная этикетка, партия 5 000</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -15664,7 +15708,7 @@
         </is>
       </c>
       <c r="E115" s="44" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="F115" s="45">
         <f>E115</f>
@@ -15683,7 +15727,7 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Вода 0,33 л в стекле, полноцветная этикетка, партия 5 000</t>
+          <t>Вода 0,33 л в стекле, полноцветная этикетка, партия 1 000</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
@@ -15692,7 +15736,7 @@
         </is>
       </c>
       <c r="E116" s="44" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="F116" s="45">
         <f>E116</f>
@@ -15711,16 +15755,16 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Доставка до объекта по Москве</t>
+          <t>Вода 0,33 л в стекле, полноцветная этикетка, партия 5 000</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E117" s="44" t="n">
-        <v>6500</v>
+        <v>110</v>
       </c>
       <c r="F117" s="45">
         <f>E117</f>
@@ -15730,35 +15774,31 @@
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Свечи и диффузоры</t>
+          <t>Брендированная вода</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Разработка эксклюзивного аромата объекта, 3 варианта на выбор</t>
+          <t>Доставка до объекта по Москве</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="E118" s="44" t="n">
-        <v>85000</v>
+        <v>6500</v>
       </c>
       <c r="F118" s="45">
         <f>E118</f>
         <v/>
       </c>
-      <c r="G118" s="8" t="inlineStr">
-        <is>
-          <t>С парфюмером производителя</t>
-        </is>
-      </c>
+      <c r="G118" s="8" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n">
@@ -15771,22 +15811,26 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Свеча 200 мл в стекле с крышкой, брендированная коробка, партия 100</t>
+          <t>Разработка эксклюзивного аромата объекта, 3 варианта на выбор</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E119" s="44" t="n">
-        <v>1350</v>
+        <v>85000</v>
       </c>
       <c r="F119" s="45">
         <f>E119</f>
         <v/>
       </c>
-      <c r="G119" s="8" t="inlineStr"/>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>С парфюмером производителя</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
@@ -15799,7 +15843,7 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Свеча 200 мл в стекле с крышкой, брендированная коробка, партия 300</t>
+          <t>Свеча 200 мл в стекле с крышкой, брендированная коробка, партия 100</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
@@ -15808,7 +15852,7 @@
         </is>
       </c>
       <c r="E120" s="44" t="n">
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="F120" s="45">
         <f>E120</f>
@@ -15827,7 +15871,7 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Диффузор 100 мл с палочками, брендированная упаковка, партия 100</t>
+          <t>Свеча 200 мл в стекле с крышкой, брендированная коробка, партия 300</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
@@ -15836,7 +15880,7 @@
         </is>
       </c>
       <c r="E121" s="44" t="n">
-        <v>1250</v>
+        <v>1150</v>
       </c>
       <c r="F121" s="45">
         <f>E121</f>
@@ -15855,7 +15899,7 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Мыло жидкое 250 мл с дозатором, брендированная этикетка, партия 300</t>
+          <t>Диффузор 100 мл с палочками, брендированная упаковка, партия 100</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
@@ -15864,7 +15908,7 @@
         </is>
       </c>
       <c r="E122" s="44" t="n">
-        <v>590</v>
+        <v>1250</v>
       </c>
       <c r="F122" s="45">
         <f>E122</f>
@@ -15883,16 +15927,16 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Доставка по Москве</t>
+          <t>Мыло жидкое 250 мл с дозатором, брендированная этикетка, партия 300</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E123" s="44" t="n">
-        <v>6500</v>
+        <v>590</v>
       </c>
       <c r="F123" s="45">
         <f>E123</f>
@@ -15902,25 +15946,25 @@
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Шоколад</t>
+          <t>Свечи и диффузоры</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Плитка шоколада 50 г, индивидуальная обертка с логотипом, партия 200</t>
+          <t>Доставка по Москве</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="E124" s="44" t="n">
-        <v>165</v>
+        <v>6500</v>
       </c>
       <c r="F124" s="45">
         <f>E124</f>
@@ -15939,7 +15983,7 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Плитка шоколада 50 г, индивидуальная обертка с логотипом, партия 1 000</t>
+          <t>Плитка шоколада 50 г, индивидуальная обертка с логотипом, партия 200</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
@@ -15948,7 +15992,7 @@
         </is>
       </c>
       <c r="E125" s="44" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="F125" s="45">
         <f>E125</f>
@@ -15967,7 +16011,7 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Набор 9 конфет в брендированной коробке, партия 200</t>
+          <t>Плитка шоколада 50 г, индивидуальная обертка с логотипом, партия 1 000</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -15976,7 +16020,7 @@
         </is>
       </c>
       <c r="E126" s="44" t="n">
-        <v>890</v>
+        <v>120</v>
       </c>
       <c r="F126" s="45">
         <f>E126</f>
@@ -15995,7 +16039,7 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Набор 9 конфет в брендированной коробке, партия 1 000</t>
+          <t>Набор 9 конфет в брендированной коробке, партия 200</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
@@ -16004,7 +16048,7 @@
         </is>
       </c>
       <c r="E127" s="44" t="n">
-        <v>720</v>
+        <v>980</v>
       </c>
       <c r="F127" s="45">
         <f>E127</f>
@@ -16023,16 +16067,16 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Дегустационный набор: плитки и конфеты из ассортимента</t>
+          <t>Набор 9 конфет в брендированной коробке, партия 1 000</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E128" s="44" t="n">
-        <v>4500</v>
+        <v>820</v>
       </c>
       <c r="F128" s="45">
         <f>E128</f>
@@ -16051,16 +16095,16 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Доставка по Москве</t>
+          <t>Дегустационный набор: плитки и конфеты из ассортимента</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E129" s="44" t="n">
-        <v>6500</v>
+        <v>4500</v>
       </c>
       <c r="F129" s="45">
         <f>E129</f>
@@ -16070,25 +16114,25 @@
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Форма для сотрудников</t>
+          <t>Шоколад</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Поло или рубашка, хлопок с эластаном</t>
+          <t>Доставка по Москве</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="E130" s="44" t="n">
-        <v>1650</v>
+        <v>6500</v>
       </c>
       <c r="F130" s="45">
         <f>E130</f>
@@ -16107,7 +16151,7 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Брюки, костюмная ткань</t>
+          <t>Поло или рубашка, хлопок с эластаном</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
@@ -16116,7 +16160,7 @@
         </is>
       </c>
       <c r="E131" s="44" t="n">
-        <v>2900</v>
+        <v>1650</v>
       </c>
       <c r="F131" s="45">
         <f>E131</f>
@@ -16135,7 +16179,7 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Жилет, костюмная ткань, подкладка</t>
+          <t>Брюки, костюмная ткань</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
@@ -16144,7 +16188,7 @@
         </is>
       </c>
       <c r="E132" s="44" t="n">
-        <v>3400</v>
+        <v>2900</v>
       </c>
       <c r="F132" s="45">
         <f>E132</f>
@@ -16163,7 +16207,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Вышивка логотипа на груди</t>
+          <t>Жилет, костюмная ткань, подкладка</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
@@ -16172,17 +16216,13 @@
         </is>
       </c>
       <c r="E133" s="44" t="n">
-        <v>350</v>
+        <v>4200</v>
       </c>
       <c r="F133" s="45">
         <f>E133</f>
         <v/>
       </c>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t>На поло и жилете</t>
-        </is>
-      </c>
+      <c r="G133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
@@ -16195,16 +16235,16 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Образец комплекта для примерки</t>
+          <t>Вышивка логотипа на груди</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E134" s="44" t="n">
-        <v>12500</v>
+        <v>350</v>
       </c>
       <c r="F134" s="45">
         <f>E134</f>
@@ -16212,7 +16252,7 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>Засчитывается в тираж</t>
+          <t>На поло и жилете</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16267,7 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>Дошив комплекта, 1-5 шт. в течение года</t>
+          <t>Образец комплекта для примерки</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
@@ -16236,26 +16276,30 @@
         </is>
       </c>
       <c r="E135" s="44" t="n">
-        <v>11900</v>
+        <v>14000</v>
       </c>
       <c r="F135" s="45">
         <f>E135</f>
         <v/>
       </c>
-      <c r="G135" s="8" t="inlineStr"/>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>Засчитывается в тираж</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Агентство по организации мероприятий</t>
+          <t>Форма для сотрудников</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Декор зоны пресс-завтрака</t>
+          <t>Дошив комплекта, 1-5 шт. в течение года</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
@@ -16264,7 +16308,7 @@
         </is>
       </c>
       <c r="E136" s="44" t="n">
-        <v>125000</v>
+        <v>12900</v>
       </c>
       <c r="F136" s="45">
         <f>E136</f>
@@ -16283,16 +16327,16 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>Кейтеринг: завтрак-фуршет, кофе-брейк, посуда, официанты</t>
+          <t>Декор зоны пресс-завтрака</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>гость</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E137" s="44" t="n">
-        <v>3600</v>
+        <v>125000</v>
       </c>
       <c r="F137" s="45">
         <f>E137</f>
@@ -16311,16 +16355,16 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Звук: акустика, 2 радиомикрофона, техник</t>
+          <t>Кейтеринг: завтрак-фуршет, кофе-брейк, посуда, официанты</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>гость</t>
         </is>
       </c>
       <c r="E138" s="44" t="n">
-        <v>32000</v>
+        <v>3800</v>
       </c>
       <c r="F138" s="45">
         <f>E138</f>
@@ -16339,16 +16383,16 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Ведущий</t>
+          <t>Звук: акустика, 2 радиомикрофона, техник</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>мероприятие</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E139" s="44" t="n">
-        <v>55000</v>
+        <v>32000</v>
       </c>
       <c r="F139" s="45">
         <f>E139</f>
@@ -16367,16 +16411,16 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Фотосъемка, 3 ч</t>
+          <t>Ведущий</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>мероприятие</t>
         </is>
       </c>
       <c r="E140" s="44" t="n">
-        <v>21000</v>
+        <v>55000</v>
       </c>
       <c r="F140" s="45">
         <f>E140</f>
@@ -16395,7 +16439,7 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Видеосъемка и отчетный ролик</t>
+          <t>Фотосъемка, 3 ч</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
@@ -16404,7 +16448,7 @@
         </is>
       </c>
       <c r="E141" s="44" t="n">
-        <v>45000</v>
+        <v>21000</v>
       </c>
       <c r="F141" s="45">
         <f>E141</f>
@@ -16423,16 +16467,16 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Welcome-подарок гостю</t>
+          <t>Видеосъемка и отчетный ролик</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E142" s="44" t="n">
-        <v>2600</v>
+        <v>45000</v>
       </c>
       <c r="F142" s="45">
         <f>E142</f>
@@ -16451,16 +16495,16 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Персонал и координация на площадке</t>
+          <t>Welcome-подарок гостю</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E143" s="44" t="n">
-        <v>32000</v>
+        <v>2600</v>
       </c>
       <c r="F143" s="45">
         <f>E143</f>
@@ -16470,16 +16514,16 @@
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Декорирование, флористика</t>
+          <t>Агентство по организации мероприятий</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Эскиз и 3D-визуализация оформления атриума</t>
+          <t>Персонал и координация на площадке</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
@@ -16488,17 +16532,13 @@
         </is>
       </c>
       <c r="E144" s="44" t="n">
-        <v>85000</v>
+        <v>32000</v>
       </c>
       <c r="F144" s="45">
-        <f>ROUND(E144*(1-Прайс!$B$6),0)</f>
-        <v/>
-      </c>
-      <c r="G144" s="8" t="inlineStr">
-        <is>
-          <t>До старта производства</t>
-        </is>
-      </c>
+        <f>E144</f>
+        <v/>
+      </c>
+      <c r="G144" s="8" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="7" t="n">
@@ -16511,25 +16551,26 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Центральная композиция высотой до 6 м, производство</t>
+          <t>Эскиз и 3D-визуализация оформления атриума</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E145" s="46" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="F145" s="47" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr"/>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E145" s="44" t="n">
+        <v>85000</v>
+      </c>
+      <c r="F145" s="45">
+        <f>ROUND(E145*(1-Прайс!$B$6),0)</f>
+        <v/>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>До старта производства</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
@@ -16542,7 +16583,7 @@
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Малая фотозона, производство</t>
+          <t>Центральная композиция высотой до 6 м, производство</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
@@ -16573,12 +16614,12 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Монтаж и демонтаж в ночное время</t>
+          <t>Малая фотозона, производство</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E147" s="46" t="inlineStr">
@@ -16604,12 +16645,12 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Хранение декора между сезонами</t>
+          <t>Монтаж и демонтаж в ночное время</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>мес.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E148" s="46" t="inlineStr">
@@ -16635,20 +16676,23 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Флористическая композиция на стол</t>
+          <t>Хранение декора между сезонами</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E149" s="44" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F149" s="45">
-        <f>E149</f>
-        <v/>
+          <t>мес.</t>
+        </is>
+      </c>
+      <c r="E149" s="46" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="F149" s="47" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
       </c>
       <c r="G149" s="8" t="inlineStr"/>
     </row>
@@ -16663,7 +16707,7 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Флористическая фотозона</t>
+          <t>Флористическая композиция на стол</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
@@ -16672,7 +16716,7 @@
         </is>
       </c>
       <c r="E150" s="44" t="n">
-        <v>95000</v>
+        <v>9500</v>
       </c>
       <c r="F150" s="45">
         <f>E150</f>
@@ -16691,16 +16735,16 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Доставка, монтаж и демонтаж флористики</t>
+          <t>Флористическая фотозона</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E151" s="44" t="n">
-        <v>16000</v>
+        <v>95000</v>
       </c>
       <c r="F151" s="45">
         <f>E151</f>
@@ -16710,25 +16754,25 @@
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Кейтеринг</t>
+          <t>Декорирование, флористика</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Завтрак-фуршет 6-8 позиций и кофе-брейк, посуда, текстиль, официанты, уборка</t>
+          <t>Доставка, монтаж и демонтаж флористики</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>гость</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E152" s="44" t="n">
-        <v>3600</v>
+        <v>16000</v>
       </c>
       <c r="F152" s="45">
         <f>E152</f>
@@ -16747,7 +16791,7 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Вечерний фуршет 10-12 позиций и безалкогольный бар, посуда, текстиль, официанты, уборка</t>
+          <t>Завтрак-фуршет 6-8 позиций и кофе-брейк, посуда, текстиль, официанты, уборка</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
@@ -16756,7 +16800,7 @@
         </is>
       </c>
       <c r="E153" s="44" t="n">
-        <v>4900</v>
+        <v>3800</v>
       </c>
       <c r="F153" s="45">
         <f>E153</f>
@@ -16775,16 +16819,16 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Официант, час (минимум 4 ч)</t>
+          <t>Вечерний фуршет 10-12 позиций и безалкогольный бар, посуда, текстиль, официанты, уборка</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>час</t>
+          <t>гость</t>
         </is>
       </c>
       <c r="E154" s="44" t="n">
-        <v>900</v>
+        <v>5300</v>
       </c>
       <c r="F154" s="45">
         <f>E154</f>
@@ -16803,39 +16847,35 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Дегустация меню на 2-3 человек</t>
+          <t>Официант, час (минимум 4 ч)</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>час</t>
         </is>
       </c>
       <c r="E155" s="44" t="n">
-        <v>15000</v>
+        <v>900</v>
       </c>
       <c r="F155" s="45">
         <f>E155</f>
         <v/>
       </c>
-      <c r="G155" s="8" t="inlineStr">
-        <is>
-          <t>Засчитывается при заказе</t>
-        </is>
-      </c>
+      <c r="G155" s="8" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Звук и свет</t>
+          <t>Кейтеринг</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Акустическая система на зону до 300 м²</t>
+          <t>Дегустация меню на 2-3 человек</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
@@ -16844,13 +16884,17 @@
         </is>
       </c>
       <c r="E156" s="44" t="n">
-        <v>28000</v>
+        <v>15000</v>
       </c>
       <c r="F156" s="45">
         <f>E156</f>
         <v/>
       </c>
-      <c r="G156" s="8" t="inlineStr"/>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t>Засчитывается при заказе</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="7" t="n">
@@ -16863,16 +16907,16 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Радиомикрофон</t>
+          <t>Акустическая система на зону до 300 м²</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E157" s="44" t="n">
-        <v>2500</v>
+        <v>28000</v>
       </c>
       <c r="F157" s="45">
         <f>E157</f>
@@ -16891,7 +16935,7 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Микшерный пульт</t>
+          <t>Радиомикрофон</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
@@ -16900,7 +16944,7 @@
         </is>
       </c>
       <c r="E158" s="44" t="n">
-        <v>6000</v>
+        <v>2800</v>
       </c>
       <c r="F158" s="45">
         <f>E158</f>
@@ -16919,16 +16963,16 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Сценический свет для подиума 4 × 3 м</t>
+          <t>Микшерный пульт</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E159" s="44" t="n">
-        <v>26000</v>
+        <v>6000</v>
       </c>
       <c r="F159" s="45">
         <f>E159</f>
@@ -16947,16 +16991,16 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Техник на все время мероприятия</t>
+          <t>Сценический свет для подиума 4 × 3 м</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E160" s="44" t="n">
-        <v>12000</v>
+        <v>26000</v>
       </c>
       <c r="F160" s="45">
         <f>E160</f>
@@ -16975,16 +17019,16 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Доставка, монтаж, демонтаж</t>
+          <t>Техник на все время мероприятия</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E161" s="44" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="F161" s="45">
         <f>E161</f>
@@ -16994,25 +17038,25 @@
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Звукорежиссер</t>
+          <t>Звук и свет</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Звукорежиссер, смена 6 ч, включая саундчек</t>
+          <t>Доставка, монтаж, демонтаж</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E162" s="44" t="n">
-        <v>22000</v>
+        <v>12000</v>
       </c>
       <c r="F162" s="45">
         <f>E162</f>
@@ -17031,54 +17075,54 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Переработка звукорежиссера</t>
+          <t>Звукорежиссер, смена 6 ч, включая саундчек</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>час</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E163" s="44" t="n">
-        <v>4000</v>
+        <v>24000</v>
       </c>
       <c r="F163" s="45">
         <f>E163</f>
         <v/>
       </c>
-      <c r="G163" s="8" t="inlineStr">
-        <is>
-          <t>Прайс</t>
-        </is>
-      </c>
+      <c r="G163" s="8" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Диджей</t>
+          <t>Звукорежиссер</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Диджей, сет 3 ч, с оборудованием</t>
+          <t>Переработка звукорежиссера</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>сет</t>
+          <t>час</t>
         </is>
       </c>
       <c r="E164" s="44" t="n">
-        <v>42000</v>
+        <v>4000</v>
       </c>
       <c r="F164" s="45">
         <f>E164</f>
         <v/>
       </c>
-      <c r="G164" s="8" t="inlineStr"/>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>Прайс</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="7" t="n">
@@ -17091,7 +17135,7 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Диджей, сет 3 ч, на оборудовании площадки</t>
+          <t>Диджей, сет 3 ч, с оборудованием</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
@@ -17100,7 +17144,7 @@
         </is>
       </c>
       <c r="E165" s="44" t="n">
-        <v>30000</v>
+        <v>42000</v>
       </c>
       <c r="F165" s="45">
         <f>E165</f>
@@ -17119,54 +17163,54 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Диджей, час (минимум 2 ч)</t>
+          <t>Диджей, сет 3 ч, на оборудовании площадки</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>час</t>
+          <t>сет</t>
         </is>
       </c>
       <c r="E166" s="44" t="n">
-        <v>11000</v>
+        <v>32000</v>
       </c>
       <c r="F166" s="45">
         <f>E166</f>
         <v/>
       </c>
-      <c r="G166" s="8" t="inlineStr">
-        <is>
-          <t>Прайс</t>
-        </is>
-      </c>
+      <c r="G166" s="8" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>Аренда мебели</t>
+          <t>Диджей</t>
         </is>
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Лаунж-зона: диван, 2 кресла, журнальный стол</t>
+          <t>Диджей, час (минимум 2 ч)</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>компл./сут.</t>
+          <t>час</t>
         </is>
       </c>
       <c r="E167" s="44" t="n">
-        <v>18000</v>
+        <v>11000</v>
       </c>
       <c r="F167" s="45">
         <f>E167</f>
         <v/>
       </c>
-      <c r="G167" s="8" t="inlineStr"/>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>Прайс</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n">
@@ -17179,16 +17223,16 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Коктейльный стол с чехлом</t>
+          <t>Лаунж-зона: диван, 2 кресла, журнальный стол</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>шт./сут.</t>
+          <t>компл./сут.</t>
         </is>
       </c>
       <c r="E168" s="44" t="n">
-        <v>2200</v>
+        <v>18000</v>
       </c>
       <c r="F168" s="45">
         <f>E168</f>
@@ -17207,7 +17251,7 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Барная стойка</t>
+          <t>Коктейльный стол с чехлом</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
@@ -17216,7 +17260,7 @@
         </is>
       </c>
       <c r="E169" s="44" t="n">
-        <v>14000</v>
+        <v>2200</v>
       </c>
       <c r="F169" s="45">
         <f>E169</f>
@@ -17235,16 +17279,16 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Доставка, сборка и вывоз в ночное время</t>
+          <t>Барная стойка</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт./сут.</t>
         </is>
       </c>
       <c r="E170" s="44" t="n">
-        <v>28000</v>
+        <v>14000</v>
       </c>
       <c r="F170" s="45">
         <f>E170</f>
@@ -17254,38 +17298,31 @@
     </row>
     <row r="171">
       <c r="A171" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>Закупка мебели</t>
+          <t>Аренда мебели</t>
         </is>
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Диван для общественной зоны, ткань от 50 000 циклов по Мартиндейлу</t>
+          <t>Доставка, сборка и вывоз в ночное время</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E171" s="46" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="F171" s="47" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="G171" s="8" t="inlineStr">
-        <is>
-          <t>Ориентир от 120 000 ₽ без НДС</t>
-        </is>
-      </c>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E171" s="44" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F171" s="45">
+        <f>E171</f>
+        <v/>
+      </c>
+      <c r="G171" s="8" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n">
@@ -17298,7 +17335,7 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Кресло для общественной зоны, та же ткань</t>
+          <t>Диван для общественной зоны, ткань от 50 000 циклов по Мартиндейлу</t>
         </is>
       </c>
       <c r="D172" s="7" t="inlineStr">
@@ -17318,7 +17355,7 @@
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>Ориентир от 50 000 ₽ без НДС</t>
+          <t>Ориентир от 120 000 ₽ без НДС</t>
         </is>
       </c>
     </row>
@@ -17333,7 +17370,7 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Столик для зоны отдыха</t>
+          <t>Кресло для общественной зоны, та же ткань</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
@@ -17353,7 +17390,7 @@
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>Ориентир от 18 000 ₽ без НДС</t>
+          <t>Ориентир от 50 000 ₽ без НДС</t>
         </is>
       </c>
     </row>
@@ -17368,12 +17405,12 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Доставка, сборка, вывоз упаковки</t>
+          <t>Столик для зоны отдыха</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E174" s="46" t="inlineStr">
@@ -17386,33 +17423,40 @@
           <t>По запросу</t>
         </is>
       </c>
-      <c r="G174" s="8" t="inlineStr"/>
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t>Ориентир от 18 000 ₽ без НДС</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>Стажеры, персонал</t>
+          <t>Закупка мебели</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Промоутер</t>
+          <t>Доставка, сборка, вывоз упаковки</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>час</t>
-        </is>
-      </c>
-      <c r="E175" s="44" t="n">
-        <v>700</v>
-      </c>
-      <c r="F175" s="45">
-        <f>E175</f>
-        <v/>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E175" s="46" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="F175" s="47" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
       </c>
       <c r="G175" s="8" t="inlineStr"/>
     </row>
@@ -17427,7 +17471,7 @@
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Хостес со знанием английского</t>
+          <t>Промоутер</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
@@ -17436,7 +17480,7 @@
         </is>
       </c>
       <c r="E176" s="44" t="n">
-        <v>1200</v>
+        <v>750</v>
       </c>
       <c r="F176" s="45">
         <f>E176</f>
@@ -17455,7 +17499,7 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Стажер</t>
+          <t>Хостес со знанием английского</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
@@ -17464,17 +17508,13 @@
         </is>
       </c>
       <c r="E177" s="44" t="n">
-        <v>550</v>
+        <v>1200</v>
       </c>
       <c r="F177" s="45">
         <f>E177</f>
         <v/>
       </c>
-      <c r="G177" s="8" t="inlineStr">
-        <is>
-          <t>Прайс</t>
-        </is>
-      </c>
+      <c r="G177" s="8" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n">
@@ -17487,7 +17527,7 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Администратор (супервайзер)</t>
+          <t>Стажер</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr">
@@ -17496,7 +17536,7 @@
         </is>
       </c>
       <c r="E178" s="44" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="F178" s="45">
         <f>E178</f>
@@ -17519,16 +17559,16 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Брендированная футболка для персонала</t>
+          <t>Администратор (супервайзер)</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>час</t>
         </is>
       </c>
       <c r="E179" s="44" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F179" s="45">
         <f>E179</f>
@@ -17536,40 +17576,41 @@
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t>Опция. Дресс-код в своей одежде бесплатно</t>
+          <t>Прайс</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>Фотозона</t>
+          <t>Стажеры, персонал</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Зеркальные панели «водная рябь» на каркасе, стена</t>
+          <t>Брендированная футболка для персонала</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="E180" s="46" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="F180" s="47" t="inlineStr">
-        <is>
-          <t>По запросу</t>
-        </is>
-      </c>
-      <c r="G180" s="8" t="inlineStr"/>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E180" s="44" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F180" s="45">
+        <f>E180</f>
+        <v/>
+      </c>
+      <c r="G180" s="8" t="inlineStr">
+        <is>
+          <t>Опция. Дресс-код в своей одежде бесплатно</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="7" t="n">
@@ -17582,7 +17623,7 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Напольное покрытие, зеркальный пластик, край волной</t>
+          <t>Зеркальные панели «водная рябь» на каркасе, стена</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
@@ -17600,11 +17641,7 @@
           <t>По запросу</t>
         </is>
       </c>
-      <c r="G181" s="8" t="inlineStr">
-        <is>
-          <t>С антискользящей защитной пленкой</t>
-        </is>
-      </c>
+      <c r="G181" s="8" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n">
@@ -17617,12 +17654,12 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Световой лайтбокс в форме логотипа 2200 × 1500 мм</t>
+          <t>Напольное покрытие, зеркальный пластик, край волной</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="E182" s="46" t="inlineStr">
@@ -17635,7 +17672,11 @@
           <t>По запросу</t>
         </is>
       </c>
-      <c r="G182" s="8" t="inlineStr"/>
+      <c r="G182" s="8" t="inlineStr">
+        <is>
+          <t>С антискользящей защитной пленкой</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="7" t="n">
@@ -17648,12 +17689,12 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Монтаж фотозоны</t>
+          <t>Световой лайтбокс в форме логотипа 2200 × 1500 мм</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E183" s="46" t="inlineStr">
@@ -17679,25 +17720,56 @@
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
+          <t>Монтаж фотозоны</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E184" s="46" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="F184" s="47" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="G184" s="8" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
+          <t>Фотозона</t>
+        </is>
+      </c>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
           <t>Демонтаж фотозоны</t>
         </is>
       </c>
-      <c r="D184" s="7" t="inlineStr">
+      <c r="D185" s="7" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="E184" s="46" t="inlineStr">
+      <c r="E185" s="46" t="inlineStr">
         <is>
           <t>По запросу</t>
         </is>
       </c>
-      <c r="F184" s="47" t="inlineStr">
+      <c r="F185" s="47" t="inlineStr">
         <is>
           <t>По запросу</t>
         </is>
       </c>
-      <c r="G184" s="8" t="inlineStr"/>
+      <c r="G185" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/mirror/for/kievskaya-ploshchad/kp.xlsx
+++ b/mirror/for/kievskaya-ploshchad/kp.xlsx
@@ -695,7 +695,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="26" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Стоимость работ</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>По каждой позиции на листе «КП», ставки на листе «Прайс»</t>
+          <t>Ориентировочный расчет по каждой позиции на листе «КП», ставки на листе «Прайс». Точную стоимость даем под конкретный проект после брифа и расчета, она фиксируется в смете или спецификации к договору. Предложение не является публичной офертой</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Скидка</t>
@@ -762,14 +762,14 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Фиксация цен</t>
         </is>
       </c>
       <c r="B12" s="5">
-        <f>"Работа агентства: "&amp;Прайс!$B$9&amp;" мес. с даты КП. Производство и закупки: "&amp;Прайс!$B$10&amp;" мес. с даты КП, дальше пересчет по ценам поставщиков"</f>
+        <f>"Ставки работы агентства: "&amp;Прайс!$B$9&amp;" мес. с даты КП при тех же параметрах задачи. Производство и закупки: ориентир на "&amp;Прайс!$B$10&amp;" мес., дальше по ценам поставщиков на дату заказа"</f>
         <v/>
       </c>
     </row>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Объекты: ТРЦ «Ривьера», Центральный рынок, МФК «Венеция», ТЦ «Времена года», ТЦ «ЦДМ на Лубянке». Расчеты по запросам ТЗ. Цены в рублях без НДС, НДС 22% начисляется сверху. Доставка в расчетах по адресу: Москва, ул. Автозаводская, д. 18.</t>
+          <t>Объекты: ТРЦ «Ривьера», Центральный рынок, МФК «Венеция», ТЦ «Времена года», ТЦ «ЦДМ на Лубянке». Расчеты по запросам ТЗ ориентировочные: точную стоимость даем под конкретный проект после брифа и расчета, она фиксируется в смете или спецификации к договору. Не является публичной офертой. Цены в рублях без НДС, НДС 22% начисляется сверху. Доставка в расчетах по адресу: Москва, ул. Автозаводская, д. 18.</t>
         </is>
       </c>
     </row>
@@ -12546,7 +12546,7 @@
     <row r="2">
       <c r="A2" s="38" t="inlineStr">
         <is>
-          <t>Цены в рублях без НДС, НДС 22% начисляется сверху. Желтые ячейки: параметры условий, от них считаются КП и сводка.</t>
+          <t>Цены в рублях без НДС, НДС 22% начисляется сверху. Цены ориентировочные, точная стоимость под проект после расчета. Желтые ячейки: параметры условий, от них считаются КП и сводка.</t>
         </is>
       </c>
     </row>

--- a/mirror/for/kievskaya-ploshchad/kp.xlsx
+++ b/mirror/for/kievskaya-ploshchad/kp.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;-#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.##"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,7 +54,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000000FF"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -65,17 +65,6 @@
     <font>
       <name val="Arial"/>
       <color rgb="00595959"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="000000FF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -107,7 +96,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -117,11 +106,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000F0F0F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -168,10 +152,10 @@
   </cellStyleXfs>
   <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -189,36 +173,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,16 +211,16 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -245,22 +229,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -272,19 +256,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1683,6 +1667,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
@@ -12509,6 +12494,7 @@
       <c r="P249" s="8" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <autoFilter ref="A4:P249"/>
   <mergeCells count="1">
     <mergeCell ref="A2:P2"/>
@@ -12546,7 +12532,7 @@
     <row r="2">
       <c r="A2" s="38" t="inlineStr">
         <is>
-          <t>Цены в рублях без НДС, НДС 22% начисляется сверху. Цены ориентировочные, точная стоимость под проект после расчета. Желтые ячейки: параметры условий, от них считаются КП и сводка.</t>
+          <t>Цены в рублях без НДС, НДС 22% начисляется сверху. Цены ориентировочные, точная стоимость под проект после расчета.</t>
         </is>
       </c>
     </row>
@@ -17772,6 +17758,7 @@
       <c r="G185" s="8" t="inlineStr"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/mirror/for/kievskaya-ploshchad/kp.xlsx
+++ b/mirror/for/kievskaya-ploshchad/kp.xlsx
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
+        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток "&amp;TEXT(1-Прайс!$B$11,"0%")&amp;" после акта"</f>
         <v/>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
         <v/>
       </c>
       <c r="E30" s="8">
-        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
+        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток "&amp;TEXT(1-Прайс!$B$11,"0%")&amp;" после акта"</f>
         <v/>
       </c>
       <c r="F30" s="8">
@@ -1485,7 +1485,7 @@
         <v/>
       </c>
       <c r="E42" s="8">
-        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
+        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток "&amp;TEXT(1-Прайс!$B$11,"0%")&amp;" после акта"</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1512,7 +1512,7 @@
         <v/>
       </c>
       <c r="E43" s="8">
-        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
+        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток "&amp;TEXT(1-Прайс!$B$11,"0%")&amp;" после акта"</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="E44" s="8">
-        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
+        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток "&amp;TEXT(1-Прайс!$B$11,"0%")&amp;" после акта"</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="E47" s="8">
-        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
+        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток "&amp;TEXT(1-Прайс!$B$11,"0%")&amp;" после акта"</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -5838,7 +5838,7 @@
       <c r="L94" s="17" t="n"/>
       <c r="M94" s="17" t="n"/>
       <c r="N94" s="17">
-        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
+        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток "&amp;TEXT(1-Прайс!$B$11,"0%")&amp;" после акта"</f>
         <v/>
       </c>
       <c r="O94" s="17">
@@ -10916,7 +10916,7 @@
       <c r="L212" s="17" t="n"/>
       <c r="M212" s="17" t="n"/>
       <c r="N212" s="17">
-        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
+        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток "&amp;TEXT(1-Прайс!$B$11,"0%")&amp;" после акта"</f>
         <v/>
       </c>
       <c r="O212" s="17">
@@ -11270,7 +11270,7 @@
       <c r="L220" s="17" t="n"/>
       <c r="M220" s="17" t="n"/>
       <c r="N220" s="17">
-        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
+        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток "&amp;TEXT(1-Прайс!$B$11,"0%")&amp;" после акта"</f>
         <v/>
       </c>
       <c r="O220" s="17">
@@ -11361,7 +11361,7 @@
       <c r="L222" s="17" t="n"/>
       <c r="M222" s="17" t="n"/>
       <c r="N222" s="17">
-        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
+        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток "&amp;TEXT(1-Прайс!$B$11,"0%")&amp;" после акта"</f>
         <v/>
       </c>
       <c r="O222" s="17">
@@ -11989,7 +11989,7 @@
       <c r="L237" s="17" t="n"/>
       <c r="M237" s="17" t="n"/>
       <c r="N237" s="17">
-        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток в течение "&amp;Прайс!$B$8&amp;" р.д. после акта"</f>
+        <f>"Аванс "&amp;TEXT(Прайс!$B$11,"0%")&amp;" на расходы подрядчиков, остаток "&amp;TEXT(1-Прайс!$B$11,"0%")&amp;" после акта"</f>
         <v/>
       </c>
       <c r="O237" s="17">
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="B11" s="41" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
